--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -5,19 +5,19 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="9"/>
   </bookViews>
   <sheets>
-    <sheet name="FRAME" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="WHEELSET" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="TIRES" sheetId="3" state="visible" r:id="rId4"/>
-    <sheet name="DISCS" sheetId="4" state="visible" r:id="rId5"/>
-    <sheet name="SHIFTERS" sheetId="5" state="visible" r:id="rId6"/>
-    <sheet name="REAR+FRONT DER" sheetId="6" state="visible" r:id="rId7"/>
-    <sheet name="CASSETTE" sheetId="7" state="visible" r:id="rId8"/>
-    <sheet name="CRANKSET" sheetId="8" state="visible" r:id="rId9"/>
-    <sheet name="SADDLE" sheetId="9" state="visible" r:id="rId10"/>
-    <sheet name="COCKPIT" sheetId="10" state="visible" r:id="rId11"/>
+    <sheet name="Frame" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Wheelset" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="Tires" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="Discs" sheetId="4" state="visible" r:id="rId5"/>
+    <sheet name="Shifters" sheetId="5" state="visible" r:id="rId6"/>
+    <sheet name="Derailleurs" sheetId="6" state="visible" r:id="rId7"/>
+    <sheet name="Cassette" sheetId="7" state="visible" r:id="rId8"/>
+    <sheet name="Crankset" sheetId="8" state="visible" r:id="rId9"/>
+    <sheet name="Saddle" sheetId="9" state="visible" r:id="rId10"/>
+    <sheet name="Cockpit" sheetId="10" state="visible" r:id="rId11"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="9"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Frame" sheetId="1" state="visible" r:id="rId2"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="27">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -55,7 +55,7 @@
     <t xml:space="preserve">Specialized</t>
   </si>
   <si>
-    <t xml:space="preserve">https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/Frame.png</t>
+    <t xml:space="preserve">https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/FrameO.png</t>
   </si>
   <si>
     <t xml:space="preserve">Madone SLR Gen 7</t>
@@ -76,7 +76,7 @@
     <t xml:space="preserve">ENVE</t>
   </si>
   <si>
-    <t xml:space="preserve">/parts/Wheel2O.png</t>
+    <t xml:space="preserve">/parts/WheelO.png</t>
   </si>
   <si>
     <t xml:space="preserve">BLACK INC</t>
@@ -85,31 +85,22 @@
     <t xml:space="preserve">BI</t>
   </si>
   <si>
-    <t xml:space="preserve">/parts/WheelO.png</t>
-  </si>
-  <si>
     <t xml:space="preserve">ZIPP</t>
   </si>
   <si>
-    <t xml:space="preserve">/parts/WheelOption2.png</t>
-  </si>
-  <si>
     <t xml:space="preserve">GP5000</t>
   </si>
   <si>
     <t xml:space="preserve">Continental</t>
   </si>
   <si>
-    <t xml:space="preserve">/parts/TireO.png</t>
+    <t xml:space="preserve">https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/TiressOO.png</t>
   </si>
   <si>
     <t xml:space="preserve">PRO ONE</t>
   </si>
   <si>
     <t xml:space="preserve">Schwalbe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/parts/Tire.png</t>
   </si>
   <si>
     <t xml:space="preserve">CENTERLINE</t>
@@ -338,9 +329,9 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/Frame.png"/>
-    <hyperlink ref="E3" r:id="rId2" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/Frame.png"/>
-    <hyperlink ref="E4" r:id="rId3" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/Frame.png"/>
+    <hyperlink ref="E2" r:id="rId1" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/FrameO.png"/>
+    <hyperlink ref="E3" r:id="rId2" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/FrameO.png"/>
+    <hyperlink ref="E4" r:id="rId3" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/FrameO.png"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
@@ -403,7 +394,9 @@
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="1" style="0" width="12.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="12.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="32.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="6" style="0" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -460,7 +453,7 @@
         <v>1350</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>2</v>
@@ -468,10 +461,10 @@
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>2599</v>
@@ -480,7 +473,7 @@
         <v>1450</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>2</v>
@@ -505,7 +498,9 @@
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="1" style="0" width="12.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="12.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="57.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="6" style="0" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -530,10 +525,10 @@
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>160</v>
@@ -542,7 +537,7 @@
         <v>520</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>3</v>
@@ -550,10 +545,10 @@
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>150</v>
@@ -562,13 +557,17 @@
         <v>499</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>3</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/TiressOO.png"/>
+    <hyperlink ref="E3" r:id="rId2" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/TiressOO.png"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
   <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -614,10 +613,10 @@
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>80</v>
@@ -626,7 +625,7 @@
         <v>320</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>4</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -284,7 +284,7 @@
         <v>8</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -304,7 +304,7 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -324,7 +324,7 @@
         <v>8</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -436,7 +436,7 @@
         <v>15</v>
       </c>
       <c r="F2" s="0" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -456,7 +456,7 @@
         <v>15</v>
       </c>
       <c r="F3" s="0" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -476,7 +476,7 @@
         <v>15</v>
       </c>
       <c r="F4" s="0" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -540,7 +540,7 @@
         <v>21</v>
       </c>
       <c r="F2" s="0" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -560,7 +560,7 @@
         <v>21</v>
       </c>
       <c r="F3" s="0" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -628,7 +628,7 @@
         <v>26</v>
       </c>
       <c r="F2" s="0" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -5,19 +5,20 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="Frame" sheetId="1" state="visible" r:id="rId2"/>
     <sheet name="Wheelset" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="Tires" sheetId="3" state="visible" r:id="rId4"/>
-    <sheet name="Discs" sheetId="4" state="visible" r:id="rId5"/>
-    <sheet name="Shifters" sheetId="5" state="visible" r:id="rId6"/>
-    <sheet name="Derailleurs" sheetId="6" state="visible" r:id="rId7"/>
-    <sheet name="Cassette" sheetId="7" state="visible" r:id="rId8"/>
+    <sheet name="Tyres" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="Cockpit" sheetId="4" state="visible" r:id="rId5"/>
+    <sheet name="Tape" sheetId="5" state="visible" r:id="rId6"/>
+    <sheet name="Saddle" sheetId="6" state="visible" r:id="rId7"/>
+    <sheet name="Shifters" sheetId="7" state="visible" r:id="rId8"/>
     <sheet name="Crankset" sheetId="8" state="visible" r:id="rId9"/>
-    <sheet name="Saddle" sheetId="9" state="visible" r:id="rId10"/>
-    <sheet name="Cockpit" sheetId="10" state="visible" r:id="rId11"/>
+    <sheet name="Derailleurs" sheetId="9" state="visible" r:id="rId10"/>
+    <sheet name="Cassette" sheetId="10" state="visible" r:id="rId11"/>
+    <sheet name="Discs" sheetId="11" state="visible" r:id="rId12"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="56">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -46,7 +47,10 @@
     <t xml:space="preserve">ImageURL</t>
   </si>
   <si>
-    <t xml:space="preserve">ZIndex</t>
+    <t xml:space="preserve">Zindex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logic</t>
   </si>
   <si>
     <t xml:space="preserve">S-Works Tarmac SL8</t>
@@ -88,6 +92,9 @@
     <t xml:space="preserve">ZIPP</t>
   </si>
   <si>
+    <t xml:space="preserve">ENVE Foundation</t>
+  </si>
+  <si>
     <t xml:space="preserve">GP5000</t>
   </si>
   <si>
@@ -103,6 +110,81 @@
     <t xml:space="preserve">Schwalbe</t>
   </si>
   <si>
+    <t xml:space="preserve">GP5000 TR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRO ONE TLR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selle Italia 142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/parts/SaddleO.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prologo 142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fizik</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dimension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pride</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sram Rival E1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sram</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/parts/ForceSHIFTO.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sram Force E1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sram RED E1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sram Force AXS E1 48/35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/parts/CranksO.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sram Force AXS E1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sram </t>
+  </si>
+  <si>
+    <t xml:space="preserve">/parts/ForceGroupO.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sram Red AXS E1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sram Rival AXS E1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sram Force AXS 10-36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/parts/CadenaOO.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sram Force AXS 10-33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sram Force AXS 10-28</t>
+  </si>
+  <si>
     <t xml:space="preserve">CENTERLINE</t>
   </si>
   <si>
@@ -110,6 +192,12 @@
   </si>
   <si>
     <t xml:space="preserve">/parts/DiscsOO.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTERLINE FORCE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTERLINE RED</t>
   </si>
 </sst>
 </file>
@@ -200,7 +288,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -221,6 +309,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -238,7 +330,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="29.98"/>
@@ -266,13 +358,16 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="0" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>5500</v>
@@ -281,18 +376,18 @@
         <v>685</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>5200</v>
@@ -301,18 +396,18 @@
         <v>750</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>6000</v>
@@ -321,10 +416,10 @@
         <v>770</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -348,14 +443,15 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="50.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="2" style="0" width="12.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="12.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="29.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="6" style="0" width="12.63"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -368,11 +464,181 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>150</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>198</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>150</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>188</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>150</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>168</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="12.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="26.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="6" style="0" width="12.63"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>80</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>180</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>90</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>160</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>140</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -391,7 +657,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="12.63"/>
@@ -418,13 +684,16 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="0" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>2099</v>
@@ -433,18 +702,18 @@
         <v>1250</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2" s="0" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>1999</v>
@@ -453,18 +722,18 @@
         <v>1350</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F3" s="0" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>2599</v>
@@ -473,10 +742,30 @@
         <v>1450</v>
       </c>
       <c r="E4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="0" t="n">
-        <v>20</v>
+      <c r="C5" s="0" t="n">
+        <v>1399</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>1510</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -495,7 +784,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="12.63"/>
@@ -522,13 +811,16 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="0" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>160</v>
@@ -537,7 +829,7 @@
         <v>520</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>20</v>
@@ -545,10 +837,10 @@
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>150</v>
@@ -557,9 +849,49 @@
         <v>499</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F3" s="0" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>180</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>560</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>170</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>550</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="0" t="n">
         <v>20</v>
       </c>
     </row>
@@ -567,6 +899,8 @@
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/TiressOO.png"/>
     <hyperlink ref="E3" r:id="rId2" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/TiressOO.png"/>
+    <hyperlink ref="E4" r:id="rId3" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/TiressOO.png"/>
+    <hyperlink ref="E5" r:id="rId4" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/TiressOO.png"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
@@ -583,12 +917,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="12.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="26.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="6" style="0" width="12.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="50.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="2" style="0" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -610,25 +943,8 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" s="0" t="n">
-        <v>80</v>
-      </c>
-      <c r="D2" s="0" t="n">
-        <v>320</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" s="0" t="n">
-        <v>10</v>
+      <c r="G1" s="0" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -647,13 +963,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="1" style="0" width="12.63"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="1" style="0" width="11.52"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -666,20 +982,23 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="0" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -689,13 +1008,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="1" style="0" width="12.63"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -708,11 +1027,114 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>120</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>190</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>140</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>170</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>160</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>150</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>180</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>135</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>140</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>170</v>
+      </c>
+      <c r="E6" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -731,13 +1153,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="1" style="0" width="12.63"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -750,11 +1172,74 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>399</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>420</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>499</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>390</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>599</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>350</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -773,13 +1258,16 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="1" style="0" width="12.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="12.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="19.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="6" style="0" width="12.63"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -792,11 +1280,34 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>855</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>350</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -815,13 +1326,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="1" style="0" width="12.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="2" style="0" width="12.63"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -834,11 +1346,74 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>449</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>420</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>650</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>360</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>349</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>490</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="67">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -53,6 +53,9 @@
     <t xml:space="preserve">Logic</t>
   </si>
   <si>
+    <t xml:space="preserve">Cardimg</t>
+  </si>
+  <si>
     <t xml:space="preserve">S-Works Tarmac SL8</t>
   </si>
   <si>
@@ -83,6 +86,9 @@
     <t xml:space="preserve">/parts/WheelO.png</t>
   </si>
   <si>
+    <t xml:space="preserve">/parts/wheel.png</t>
+  </si>
+  <si>
     <t xml:space="preserve">BLACK INC</t>
   </si>
   <si>
@@ -104,6 +110,9 @@
     <t xml:space="preserve">https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/TiressOO.png</t>
   </si>
   <si>
+    <t xml:space="preserve">/parts/GP500.png</t>
+  </si>
+  <si>
     <t xml:space="preserve">PRO ONE</t>
   </si>
   <si>
@@ -125,6 +134,9 @@
     <t xml:space="preserve">/parts/SaddleO.png</t>
   </si>
   <si>
+    <t xml:space="preserve">/parts/Saddle.png</t>
+  </si>
+  <si>
     <t xml:space="preserve">Prologo 142</t>
   </si>
   <si>
@@ -146,6 +158,9 @@
     <t xml:space="preserve">/parts/ForceSHIFTO.png</t>
   </si>
   <si>
+    <t xml:space="preserve">/parts/sHIFTER8100.png</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sram Force E1</t>
   </si>
   <si>
@@ -155,7 +170,16 @@
     <t xml:space="preserve">Sram Force AXS E1 48/35</t>
   </si>
   <si>
-    <t xml:space="preserve">/parts/CranksO.png</t>
+    <t xml:space="preserve">/parts/ForceCrankOO.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/parts/CranksForce AXS.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sram Rival AXS E1 48/35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sram RED AXS E1 48/35</t>
   </si>
   <si>
     <t xml:space="preserve">Sram Force AXS E1</t>
@@ -167,6 +191,9 @@
     <t xml:space="preserve">/parts/ForceGroupO.png</t>
   </si>
   <si>
+    <t xml:space="preserve">/parts/AXSRDE1.png</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sram Red AXS E1</t>
   </si>
   <si>
@@ -179,6 +206,9 @@
     <t xml:space="preserve">/parts/CadenaOO.png</t>
   </si>
   <si>
+    <t xml:space="preserve">/parts/Sram_Red.png</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sram Force AXS 10-33</t>
   </si>
   <si>
@@ -192,6 +222,9 @@
   </si>
   <si>
     <t xml:space="preserve">/parts/DiscsOO.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/parts/DISCSRAM.png</t>
   </si>
   <si>
     <t xml:space="preserve">CENTERLINE FORCE</t>
@@ -207,7 +240,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -244,6 +277,12 @@
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
   </fonts>
   <fills count="2">
@@ -288,7 +327,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -303,6 +342,10 @@
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -330,7 +373,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="29.98"/>
@@ -361,13 +404,16 @@
       <c r="G1" s="0" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>5500</v>
@@ -376,18 +422,21 @@
         <v>685</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>40</v>
       </c>
+      <c r="H2" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>5200</v>
@@ -396,18 +445,21 @@
         <v>750</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>40</v>
       </c>
+      <c r="H3" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>6000</v>
@@ -416,17 +468,23 @@
         <v>770</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>40</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/FrameO.png"/>
-    <hyperlink ref="E3" r:id="rId2" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/FrameO.png"/>
-    <hyperlink ref="E4" r:id="rId3" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/FrameO.png"/>
+    <hyperlink ref="H2" r:id="rId2" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/FrameO.png"/>
+    <hyperlink ref="E3" r:id="rId3" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/FrameO.png"/>
+    <hyperlink ref="H3" r:id="rId4" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/FrameO.png"/>
+    <hyperlink ref="E4" r:id="rId5" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/FrameO.png"/>
+    <hyperlink ref="H4" r:id="rId6" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/FrameO.png"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
@@ -443,11 +501,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="12.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="29.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="29.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="6" style="0" width="12.63"/>
   </cols>
   <sheetData>
@@ -473,13 +531,16 @@
       <c r="G1" s="0" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>150</v>
@@ -488,18 +549,21 @@
         <v>198</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>30</v>
       </c>
+      <c r="H2" s="0" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>150</v>
@@ -508,18 +572,21 @@
         <v>188</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>30</v>
       </c>
+      <c r="H3" s="0" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>150</v>
@@ -528,10 +595,13 @@
         <v>168</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>30</v>
+      </c>
+      <c r="H4" s="0" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -550,7 +620,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="12.63"/>
@@ -580,13 +650,16 @@
       <c r="G1" s="0" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>80</v>
@@ -594,19 +667,22 @@
       <c r="D2" s="0" t="n">
         <v>180</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>53</v>
+      <c r="E2" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>10</v>
       </c>
+      <c r="H2" s="0" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>90</v>
@@ -614,19 +690,22 @@
       <c r="D3" s="0" t="n">
         <v>160</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>53</v>
+      <c r="E3" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>10</v>
       </c>
+      <c r="H3" s="0" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>100</v>
@@ -634,11 +713,14 @@
       <c r="D4" s="0" t="n">
         <v>140</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>53</v>
+      <c r="E4" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>10</v>
+      </c>
+      <c r="H4" s="0" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -657,7 +739,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="12.63"/>
@@ -687,13 +769,16 @@
       <c r="G1" s="0" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>2099</v>
@@ -701,19 +786,22 @@
       <c r="D2" s="0" t="n">
         <v>1250</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>16</v>
+      <c r="E2" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>30</v>
       </c>
+      <c r="H2" s="0" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>1999</v>
@@ -721,19 +809,22 @@
       <c r="D3" s="0" t="n">
         <v>1350</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>16</v>
+      <c r="E3" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>30</v>
       </c>
+      <c r="H3" s="0" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>2599</v>
@@ -741,19 +832,22 @@
       <c r="D4" s="0" t="n">
         <v>1450</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>16</v>
+      <c r="E4" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>30</v>
       </c>
+      <c r="H4" s="0" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>1399</v>
@@ -761,11 +855,14 @@
       <c r="D5" s="0" t="n">
         <v>1510</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>16</v>
+      <c r="E5" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="F5" s="0" t="n">
         <v>30</v>
+      </c>
+      <c r="H5" s="0" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -784,7 +881,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="12.63"/>
@@ -814,13 +911,16 @@
       <c r="G1" s="0" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>160</v>
@@ -828,19 +928,22 @@
       <c r="D2" s="0" t="n">
         <v>520</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>23</v>
+      <c r="E2" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>20</v>
       </c>
+      <c r="H2" s="0" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>150</v>
@@ -848,19 +951,22 @@
       <c r="D3" s="0" t="n">
         <v>499</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>23</v>
+      <c r="E3" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>20</v>
       </c>
+      <c r="H3" s="0" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>180</v>
@@ -868,19 +974,22 @@
       <c r="D4" s="0" t="n">
         <v>560</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>23</v>
+      <c r="E4" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>20</v>
       </c>
+      <c r="H4" s="0" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>170</v>
@@ -888,11 +997,14 @@
       <c r="D5" s="0" t="n">
         <v>550</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>23</v>
+      <c r="E5" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="F5" s="0" t="n">
         <v>20</v>
+      </c>
+      <c r="H5" s="0" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -917,7 +1029,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="50.63"/>
@@ -945,6 +1057,9 @@
       </c>
       <c r="G1" s="0" t="s">
         <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -963,7 +1078,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="1" style="0" width="11.52"/>
@@ -990,6 +1105,9 @@
       </c>
       <c r="G1" s="0" t="s">
         <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1008,7 +1126,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="1" style="0" width="12.63"/>
@@ -1036,13 +1154,16 @@
       <c r="G1" s="0" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>120</v>
@@ -1051,18 +1172,21 @@
         <v>190</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>10</v>
       </c>
+      <c r="H2" s="0" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>140</v>
@@ -1071,18 +1195,21 @@
         <v>170</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>10</v>
       </c>
+      <c r="H3" s="0" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="0" t="s">
         <v>32</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>29</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>160</v>
@@ -1091,18 +1218,21 @@
         <v>150</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>10</v>
       </c>
+      <c r="H4" s="0" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>180</v>
@@ -1111,18 +1241,21 @@
         <v>135</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F5" s="0" t="n">
         <v>10</v>
       </c>
+      <c r="H5" s="0" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C6" s="0" t="n">
         <v>140</v>
@@ -1131,10 +1264,13 @@
         <v>170</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F6" s="0" t="n">
         <v>10</v>
+      </c>
+      <c r="H6" s="0" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1153,7 +1289,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="1" style="0" width="12.63"/>
@@ -1181,13 +1317,16 @@
       <c r="G1" s="0" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>399</v>
@@ -1196,18 +1335,21 @@
         <v>420</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>30</v>
       </c>
+      <c r="H2" s="0" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>499</v>
@@ -1216,18 +1358,21 @@
         <v>390</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>30</v>
       </c>
+      <c r="H3" s="0" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>599</v>
@@ -1236,10 +1381,13 @@
         <v>350</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>30</v>
+      </c>
+      <c r="H4" s="0" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1258,7 +1406,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30.32"/>
@@ -1289,25 +1437,77 @@
       <c r="G1" s="0" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="0" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="0" t="s">
-        <v>36</v>
-      </c>
       <c r="C2" s="0" t="n">
-        <v>855</v>
+        <v>400</v>
       </c>
       <c r="D2" s="0" t="n">
         <v>350</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>41</v>
+      <c r="E2" s="6" t="s">
+        <v>46</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>50</v>
+      </c>
+      <c r="H2" s="0" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>799</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>320</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="H3" s="0" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>999</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>280</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="H4" s="0" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1326,7 +1526,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20.37"/>
@@ -1355,13 +1555,16 @@
       <c r="G1" s="0" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>449</v>
@@ -1370,18 +1573,21 @@
         <v>420</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>50</v>
       </c>
+      <c r="H2" s="0" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>650</v>
@@ -1390,18 +1596,21 @@
         <v>360</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>50</v>
       </c>
+      <c r="H3" s="0" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>349</v>
@@ -1410,10 +1619,13 @@
         <v>490</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>50</v>
+      </c>
+      <c r="H4" s="0" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="10"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Frame" sheetId="1" state="visible" r:id="rId2"/>
@@ -158,7 +158,7 @@
     <t xml:space="preserve">/parts/ForceSHIFTO.png</t>
   </si>
   <si>
-    <t xml:space="preserve">/parts/sHIFTER8100.png</t>
+    <t xml:space="preserve">/parts/ForceE1Shift.png</t>
   </si>
   <si>
     <t xml:space="preserve">Sram Force E1</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">/parts/ForceCrankOO.png</t>
   </si>
   <si>
-    <t xml:space="preserve">/parts/CranksForce AXS.png</t>
+    <t xml:space="preserve">/parts/ForceE1.png</t>
   </si>
   <si>
     <t xml:space="preserve">Sram Rival AXS E1 48/35</t>
@@ -344,7 +344,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -352,7 +352,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -505,7 +505,7 @@
   <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="12.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="29.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="29.37"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="6" style="0" width="12.63"/>
   </cols>
   <sheetData>
@@ -1454,13 +1454,13 @@
       <c r="D2" s="0" t="n">
         <v>350</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="4" t="s">
         <v>46</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="H2" s="0" t="s">
+      <c r="H2" s="6" t="s">
         <v>47</v>
       </c>
     </row>
@@ -1477,13 +1477,13 @@
       <c r="D3" s="0" t="n">
         <v>320</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="4" t="s">
         <v>46</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="H3" s="0" t="s">
+      <c r="H3" s="6" t="s">
         <v>47</v>
       </c>
     </row>
@@ -1500,13 +1500,13 @@
       <c r="D4" s="0" t="n">
         <v>280</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="4" t="s">
         <v>46</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="H4" s="0" t="s">
+      <c r="H4" s="6" t="s">
         <v>47</v>
       </c>
     </row>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="7"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Frame" sheetId="1" state="visible" r:id="rId2"/>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">ENVE</t>
   </si>
   <si>
-    <t xml:space="preserve">/parts/WheelO.png</t>
+    <t xml:space="preserve">https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/WheelO.png</t>
   </si>
   <si>
     <t xml:space="preserve">/parts/wheel.png</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">Selle</t>
   </si>
   <si>
-    <t xml:space="preserve">/parts/SaddleO.png</t>
+    <t xml:space="preserve">https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/SaddleO.png</t>
   </si>
   <si>
     <t xml:space="preserve">/parts/Saddle.png</t>
@@ -155,7 +155,7 @@
     <t xml:space="preserve">Sram</t>
   </si>
   <si>
-    <t xml:space="preserve">/parts/ForceSHIFTO.png</t>
+    <t xml:space="preserve">https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/ForceSHIFTO.png</t>
   </si>
   <si>
     <t xml:space="preserve">/parts/ForceE1Shift.png</t>
@@ -170,7 +170,7 @@
     <t xml:space="preserve">Sram Force AXS E1 48/35</t>
   </si>
   <si>
-    <t xml:space="preserve">/parts/ForceCrankOO.png</t>
+    <t xml:space="preserve">https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/ForceCrankOO.png</t>
   </si>
   <si>
     <t xml:space="preserve">/parts/ForceE1.png</t>
@@ -188,7 +188,7 @@
     <t xml:space="preserve">Sram </t>
   </si>
   <si>
-    <t xml:space="preserve">/parts/ForceGroupO.png</t>
+    <t xml:space="preserve">https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/ForceGroupO.png</t>
   </si>
   <si>
     <t xml:space="preserve">/parts/AXSRDE1.png</t>
@@ -203,7 +203,7 @@
     <t xml:space="preserve">Sram Force AXS 10-36</t>
   </si>
   <si>
-    <t xml:space="preserve">/parts/CadenaOO.png</t>
+    <t xml:space="preserve">https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/CadenaOO.png</t>
   </si>
   <si>
     <t xml:space="preserve">/parts/Sram_Red.png</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">SRAM</t>
   </si>
   <si>
-    <t xml:space="preserve">/parts/DiscsOO.png</t>
+    <t xml:space="preserve">https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/DiscsOO.png</t>
   </si>
   <si>
     <t xml:space="preserve">/parts/DISCSRAM.png</t>
@@ -240,7 +240,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -272,6 +272,14 @@
     </font>
     <font>
       <u val="single"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -327,7 +335,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -353,6 +361,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -501,7 +513,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="12.63"/>
@@ -604,7 +616,13 @@
         <v>58</v>
       </c>
     </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/CadenaOO.png"/>
+    <hyperlink ref="E3" r:id="rId2" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/CadenaOO.png"/>
+    <hyperlink ref="E4" r:id="rId3" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/CadenaOO.png"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
   <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -724,6 +742,11 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/DiscsOO.png"/>
+    <hyperlink ref="E3" r:id="rId2" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/DiscsOO.png"/>
+    <hyperlink ref="E4" r:id="rId3" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/DiscsOO.png"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
   <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -866,6 +889,12 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/WheelO.png"/>
+    <hyperlink ref="E3" r:id="rId2" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/WheelO.png"/>
+    <hyperlink ref="E4" r:id="rId3" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/WheelO.png"/>
+    <hyperlink ref="E5" r:id="rId4" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/WheelO.png"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
   <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1274,6 +1303,13 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/SaddleO.png"/>
+    <hyperlink ref="E3" r:id="rId2" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/SaddleO.png"/>
+    <hyperlink ref="E4" r:id="rId3" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/SaddleO.png"/>
+    <hyperlink ref="E5" r:id="rId4" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/SaddleO.png"/>
+    <hyperlink ref="E6" r:id="rId5" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/SaddleO.png"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
   <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1391,6 +1427,11 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/ForceSHIFTO.png"/>
+    <hyperlink ref="E3" r:id="rId2" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/ForceSHIFTO.png"/>
+    <hyperlink ref="E4" r:id="rId3" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/ForceSHIFTO.png"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
   <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1454,13 +1495,13 @@
       <c r="D2" s="0" t="n">
         <v>350</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="6" t="s">
         <v>46</v>
       </c>
       <c r="F2" s="0" t="n">
-        <v>50</v>
-      </c>
-      <c r="H2" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>47</v>
       </c>
     </row>
@@ -1477,13 +1518,13 @@
       <c r="D3" s="0" t="n">
         <v>320</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="6" t="s">
         <v>46</v>
       </c>
       <c r="F3" s="0" t="n">
-        <v>50</v>
-      </c>
-      <c r="H3" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>47</v>
       </c>
     </row>
@@ -1500,17 +1541,22 @@
       <c r="D4" s="0" t="n">
         <v>280</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="6" t="s">
         <v>46</v>
       </c>
       <c r="F4" s="0" t="n">
-        <v>50</v>
-      </c>
-      <c r="H4" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>47</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/ForceCrankOO.png"/>
+    <hyperlink ref="E3" r:id="rId2" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/ForceCrankOO.png"/>
+    <hyperlink ref="E4" r:id="rId3" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/ForceCrankOO.png"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
   <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1572,7 +1618,7 @@
       <c r="D2" s="0" t="n">
         <v>420</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="7" t="s">
         <v>52</v>
       </c>
       <c r="F2" s="0" t="n">
@@ -1595,7 +1641,7 @@
       <c r="D3" s="0" t="n">
         <v>360</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="7" t="s">
         <v>52</v>
       </c>
       <c r="F3" s="0" t="n">
@@ -1618,7 +1664,7 @@
       <c r="D4" s="0" t="n">
         <v>490</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="7" t="s">
         <v>52</v>
       </c>
       <c r="F4" s="0" t="n">
@@ -1629,6 +1675,11 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/ForceGroupO.png"/>
+    <hyperlink ref="E3" r:id="rId2" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/ForceGroupO.png"/>
+    <hyperlink ref="E4" r:id="rId3" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/ForceGroupO.png"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
   <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Frame" sheetId="1" state="visible" r:id="rId2"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="79">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -65,6 +65,9 @@
     <t xml:space="preserve">https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/FrameO.png</t>
   </si>
   <si>
+    <t xml:space="preserve">/parts/Frame.png</t>
+  </si>
+  <si>
     <t xml:space="preserve">Madone SLR Gen 7</t>
   </si>
   <si>
@@ -123,6 +126,39 @@
   </si>
   <si>
     <t xml:space="preserve">PRO ONE TLR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black Inc AM 90-420</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black Inc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/parts/BLACKINCBAR.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black Inc AM 90-400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black Inc AM 100-420</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black Inc AM 110-420</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DSP BARE TAPE 2.2 GRIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIZARD SKIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/parts/LZSGR.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DSP BARE TAPE 2.2 FLOUR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DSP BARE TAPE 2.2 GREEN</t>
   </si>
   <si>
     <t xml:space="preserve">Selle Italia 142</t>
@@ -240,7 +276,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -286,12 +322,6 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -335,7 +365,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -364,10 +394,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -391,7 +417,9 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="29.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="12.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="38.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="6" style="0" width="12.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="12.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="19.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="9" style="0" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -440,15 +468,15 @@
         <v>40</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>5200</v>
@@ -463,15 +491,15 @@
         <v>40</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>6000</v>
@@ -486,17 +514,14 @@
         <v>40</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/FrameO.png"/>
-    <hyperlink ref="H2" r:id="rId2" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/FrameO.png"/>
-    <hyperlink ref="E3" r:id="rId3" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/FrameO.png"/>
-    <hyperlink ref="H3" r:id="rId4" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/FrameO.png"/>
-    <hyperlink ref="E4" r:id="rId5" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/FrameO.png"/>
-    <hyperlink ref="H4" r:id="rId6" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/FrameO.png"/>
+    <hyperlink ref="E3" r:id="rId2" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/FrameO.png"/>
+    <hyperlink ref="E4" r:id="rId3" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/FrameO.png"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
@@ -549,10 +574,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>150</v>
@@ -561,21 +586,21 @@
         <v>198</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>30</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>150</v>
@@ -584,21 +609,21 @@
         <v>188</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>30</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>150</v>
@@ -607,13 +632,13 @@
         <v>168</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>30</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -674,10 +699,10 @@
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>80</v>
@@ -686,21 +711,21 @@
         <v>180</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>10</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>90</v>
@@ -709,21 +734,21 @@
         <v>160</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>10</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>100</v>
@@ -732,13 +757,13 @@
         <v>140</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>10</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -798,10 +823,10 @@
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>2099</v>
@@ -810,21 +835,21 @@
         <v>1250</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>30</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>1999</v>
@@ -833,21 +858,21 @@
         <v>1350</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>30</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>2599</v>
@@ -856,21 +881,21 @@
         <v>1450</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>30</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>1399</v>
@@ -879,13 +904,13 @@
         <v>1510</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F5" s="0" t="n">
         <v>30</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -946,10 +971,10 @@
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>160</v>
@@ -958,21 +983,21 @@
         <v>520</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>20</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>150</v>
@@ -981,21 +1006,21 @@
         <v>499</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>20</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>180</v>
@@ -1004,21 +1029,21 @@
         <v>560</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>20</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>170</v>
@@ -1027,13 +1052,13 @@
         <v>550</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F5" s="0" t="n">
         <v>20</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1058,7 +1083,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="50.63"/>
@@ -1091,6 +1116,143 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>499</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>185</v>
+      </c>
+      <c r="H2" s="0" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>499</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>185</v>
+      </c>
+      <c r="H3" s="0" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>499</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>185</v>
+      </c>
+      <c r="H4" s="0" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>499</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>185</v>
+      </c>
+      <c r="H5" s="0" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>499</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>185</v>
+      </c>
+      <c r="H6" s="0" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>499</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>185</v>
+      </c>
+      <c r="H7" s="0" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="0" t="n">
+        <v>499</v>
+      </c>
+      <c r="D8" s="0" t="n">
+        <v>185</v>
+      </c>
+      <c r="H8" s="0" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="0" t="n">
+        <v>499</v>
+      </c>
+      <c r="D9" s="0" t="n">
+        <v>185</v>
+      </c>
+      <c r="H9" s="0" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
@@ -1107,10 +1269,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="1" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="25.99"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="2" style="0" width="11.52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1137,6 +1300,57 @@
       </c>
       <c r="H1" s="4" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>68</v>
+      </c>
+      <c r="H2" s="0" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>68</v>
+      </c>
+      <c r="H3" s="0" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>68</v>
+      </c>
+      <c r="H4" s="0" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1189,10 +1403,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>120</v>
@@ -1201,21 +1415,21 @@
         <v>190</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>10</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>140</v>
@@ -1224,21 +1438,21 @@
         <v>170</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>10</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>160</v>
@@ -1247,21 +1461,21 @@
         <v>150</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>10</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>180</v>
@@ -1270,21 +1484,21 @@
         <v>135</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="F5" s="0" t="n">
         <v>10</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="C6" s="0" t="n">
         <v>140</v>
@@ -1293,13 +1507,13 @@
         <v>170</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="F6" s="0" t="n">
         <v>10</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1359,10 +1573,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>399</v>
@@ -1371,21 +1585,21 @@
         <v>420</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>30</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>499</v>
@@ -1394,21 +1608,21 @@
         <v>390</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>30</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>599</v>
@@ -1417,13 +1631,13 @@
         <v>350</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>30</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1484,10 +1698,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>400</v>
@@ -1496,21 +1710,21 @@
         <v>350</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>60</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>799</v>
@@ -1519,21 +1733,21 @@
         <v>320</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>60</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>999</v>
@@ -1542,13 +1756,13 @@
         <v>280</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>60</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1607,10 +1821,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>449</v>
@@ -1618,22 +1832,22 @@
       <c r="D2" s="0" t="n">
         <v>420</v>
       </c>
-      <c r="E2" s="7" t="s">
-        <v>52</v>
+      <c r="E2" s="4" t="s">
+        <v>64</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>50</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>650</v>
@@ -1641,22 +1855,22 @@
       <c r="D3" s="0" t="n">
         <v>360</v>
       </c>
-      <c r="E3" s="7" t="s">
-        <v>52</v>
+      <c r="E3" s="4" t="s">
+        <v>64</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>50</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>349</v>
@@ -1664,14 +1878,14 @@
       <c r="D4" s="0" t="n">
         <v>490</v>
       </c>
-      <c r="E4" s="7" t="s">
-        <v>52</v>
+      <c r="E4" s="4" t="s">
+        <v>64</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>50</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="80">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -132,6 +132,9 @@
   </si>
   <si>
     <t xml:space="preserve">Black Inc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/NADA.png</t>
   </si>
   <si>
     <t xml:space="preserve">/parts/BLACKINCBAR.png</t>
@@ -418,7 +421,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="12.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="38.44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="12.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="19.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="19.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="9" style="0" width="12.63"/>
   </cols>
   <sheetData>
@@ -574,10 +577,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>150</v>
@@ -586,21 +589,21 @@
         <v>198</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>30</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>150</v>
@@ -609,21 +612,21 @@
         <v>188</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>30</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>150</v>
@@ -632,13 +635,13 @@
         <v>168</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>30</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -699,10 +702,10 @@
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>80</v>
@@ -711,21 +714,21 @@
         <v>180</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>10</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>90</v>
@@ -734,21 +737,21 @@
         <v>160</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>10</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>100</v>
@@ -757,13 +760,13 @@
         <v>140</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>10</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -1129,13 +1132,19 @@
       <c r="D2" s="0" t="n">
         <v>185</v>
       </c>
+      <c r="E2" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>10</v>
+      </c>
       <c r="H2" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B3" s="0" t="s">
         <v>33</v>
@@ -1146,13 +1155,19 @@
       <c r="D3" s="0" t="n">
         <v>185</v>
       </c>
+      <c r="E3" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>10</v>
+      </c>
       <c r="H3" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B4" s="0" t="s">
         <v>33</v>
@@ -1163,13 +1178,19 @@
       <c r="D4" s="0" t="n">
         <v>185</v>
       </c>
+      <c r="E4" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>10</v>
+      </c>
       <c r="H4" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B5" s="0" t="s">
         <v>33</v>
@@ -1180,8 +1201,14 @@
       <c r="D5" s="0" t="n">
         <v>185</v>
       </c>
+      <c r="E5" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>10</v>
+      </c>
       <c r="H5" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1197,13 +1224,19 @@
       <c r="D6" s="0" t="n">
         <v>185</v>
       </c>
+      <c r="E6" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>10</v>
+      </c>
       <c r="H6" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B7" s="0" t="s">
         <v>33</v>
@@ -1214,13 +1247,19 @@
       <c r="D7" s="0" t="n">
         <v>185</v>
       </c>
+      <c r="E7" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>10</v>
+      </c>
       <c r="H7" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B8" s="0" t="s">
         <v>33</v>
@@ -1231,13 +1270,19 @@
       <c r="D8" s="0" t="n">
         <v>185</v>
       </c>
+      <c r="E8" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" s="0" t="n">
+        <v>10</v>
+      </c>
       <c r="H8" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9" s="0" t="s">
         <v>33</v>
@@ -1248,12 +1293,28 @@
       <c r="D9" s="0" t="n">
         <v>185</v>
       </c>
+      <c r="E9" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" s="0" t="n">
+        <v>10</v>
+      </c>
       <c r="H9" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/NADA.png"/>
+    <hyperlink ref="E3" r:id="rId2" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/NADA.png"/>
+    <hyperlink ref="E4" r:id="rId3" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/NADA.png"/>
+    <hyperlink ref="E5" r:id="rId4" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/NADA.png"/>
+    <hyperlink ref="E6" r:id="rId5" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/NADA.png"/>
+    <hyperlink ref="E7" r:id="rId6" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/NADA.png"/>
+    <hyperlink ref="E8" r:id="rId7" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/NADA.png"/>
+    <hyperlink ref="E9" r:id="rId8" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/NADA.png"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
   <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1304,10 +1365,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>34.99</v>
@@ -1315,16 +1376,22 @@
       <c r="D2" s="0" t="n">
         <v>68</v>
       </c>
+      <c r="E2" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>10</v>
+      </c>
       <c r="H2" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>34.99</v>
@@ -1332,16 +1399,22 @@
       <c r="D3" s="0" t="n">
         <v>68</v>
       </c>
+      <c r="E3" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>10</v>
+      </c>
       <c r="H3" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>34.99</v>
@@ -1349,11 +1422,22 @@
       <c r="D4" s="0" t="n">
         <v>68</v>
       </c>
+      <c r="E4" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>10</v>
+      </c>
       <c r="H4" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/NADA.png"/>
+    <hyperlink ref="E3" r:id="rId2" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/NADA.png"/>
+    <hyperlink ref="E4" r:id="rId3" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/NADA.png"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1403,10 +1487,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>120</v>
@@ -1415,21 +1499,21 @@
         <v>190</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>10</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>140</v>
@@ -1438,21 +1522,21 @@
         <v>170</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>10</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>160</v>
@@ -1461,21 +1545,21 @@
         <v>150</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>10</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>180</v>
@@ -1484,21 +1568,21 @@
         <v>135</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F5" s="0" t="n">
         <v>10</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C6" s="0" t="n">
         <v>140</v>
@@ -1507,13 +1591,13 @@
         <v>170</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F6" s="0" t="n">
         <v>10</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1573,10 +1657,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>399</v>
@@ -1585,21 +1669,21 @@
         <v>420</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>30</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>499</v>
@@ -1608,21 +1692,21 @@
         <v>390</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>30</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>599</v>
@@ -1631,13 +1715,13 @@
         <v>350</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>30</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -1698,10 +1782,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>400</v>
@@ -1710,21 +1794,21 @@
         <v>350</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>60</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>799</v>
@@ -1733,21 +1817,21 @@
         <v>320</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>60</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>999</v>
@@ -1756,13 +1840,13 @@
         <v>280</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>60</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1821,10 +1905,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>449</v>
@@ -1833,21 +1917,21 @@
         <v>420</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>50</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>650</v>
@@ -1856,21 +1940,21 @@
         <v>360</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>50</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>349</v>
@@ -1879,13 +1963,13 @@
         <v>490</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>50</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Frame" sheetId="1" state="visible" r:id="rId2"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="82">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -155,13 +155,19 @@
     <t xml:space="preserve">LIZARD SKIN</t>
   </si>
   <si>
+    <t xml:space="preserve">/parts/lizard-skins-dsp-bar-tape-v2-2.5mm-369874-12.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DSP BARE TAPE 2.2 FLOUR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/parts/lizard-skins-dsp-bar-tape-v2-2.5mm-369874-17.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DSP BARE TAPE 2.2 GREEN</t>
+  </si>
+  <si>
     <t xml:space="preserve">/parts/LZSGR.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP BARE TAPE 2.2 FLOUR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP BARE TAPE 2.2 GREEN</t>
   </si>
   <si>
     <t xml:space="preserve">Selle Italia 142</t>
@@ -421,7 +427,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="12.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="38.44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="12.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="19.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="19.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="9" style="0" width="12.63"/>
   </cols>
   <sheetData>
@@ -577,10 +583,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>150</v>
@@ -589,21 +595,21 @@
         <v>198</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>30</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>150</v>
@@ -612,21 +618,21 @@
         <v>188</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>30</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>150</v>
@@ -635,13 +641,13 @@
         <v>168</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>30</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -702,10 +708,10 @@
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>80</v>
@@ -714,21 +720,21 @@
         <v>180</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>10</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>90</v>
@@ -737,21 +743,21 @@
         <v>160</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>10</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>100</v>
@@ -760,13 +766,13 @@
         <v>140</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>10</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -1406,12 +1412,12 @@
         <v>10</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B4" s="0" t="s">
         <v>40</v>
@@ -1429,7 +1435,7 @@
         <v>10</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1487,10 +1493,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>120</v>
@@ -1499,21 +1505,21 @@
         <v>190</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>10</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>140</v>
@@ -1522,21 +1528,21 @@
         <v>170</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>10</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>160</v>
@@ -1545,21 +1551,21 @@
         <v>150</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>10</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>180</v>
@@ -1568,21 +1574,21 @@
         <v>135</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F5" s="0" t="n">
         <v>10</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C6" s="0" t="n">
         <v>140</v>
@@ -1591,13 +1597,13 @@
         <v>170</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F6" s="0" t="n">
         <v>10</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1657,10 +1663,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>399</v>
@@ -1669,21 +1675,21 @@
         <v>420</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>30</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>499</v>
@@ -1692,21 +1698,21 @@
         <v>390</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>30</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>599</v>
@@ -1715,13 +1721,13 @@
         <v>350</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>30</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1782,10 +1788,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>400</v>
@@ -1794,21 +1800,21 @@
         <v>350</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>60</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>799</v>
@@ -1817,21 +1823,21 @@
         <v>320</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>60</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>999</v>
@@ -1840,13 +1846,13 @@
         <v>280</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>60</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1905,10 +1911,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>449</v>
@@ -1917,21 +1923,21 @@
         <v>420</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>50</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>650</v>
@@ -1940,21 +1946,21 @@
         <v>360</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>50</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>349</v>
@@ -1963,13 +1969,13 @@
         <v>490</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>50</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Frame" sheetId="1" state="visible" r:id="rId2"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="94">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -50,12 +50,12 @@
     <t xml:space="preserve">Zindex</t>
   </si>
   <si>
+    <t xml:space="preserve">Cardimg</t>
+  </si>
+  <si>
     <t xml:space="preserve">Logic</t>
   </si>
   <si>
-    <t xml:space="preserve">Cardimg</t>
-  </si>
-  <si>
     <t xml:space="preserve">S-Works Tarmac SL8</t>
   </si>
   <si>
@@ -68,12 +68,18 @@
     <t xml:space="preserve">/parts/Frame.png</t>
   </si>
   <si>
+    <t xml:space="preserve">A</t>
+  </si>
+  <si>
     <t xml:space="preserve">Madone SLR Gen 7</t>
   </si>
   <si>
     <t xml:space="preserve">Trek</t>
   </si>
   <si>
+    <t xml:space="preserve">B</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lab71 SuperSix EVO</t>
   </si>
   <si>
@@ -206,12 +212,30 @@
     <t xml:space="preserve">/parts/ForceE1Shift.png</t>
   </si>
   <si>
+    <t xml:space="preserve">Sr</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sram Force E1</t>
   </si>
   <si>
     <t xml:space="preserve">Sram RED E1</t>
   </si>
   <si>
+    <t xml:space="preserve">105 Di2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shimano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ultegra R8170</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Dura Ace R9120</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sram Force AXS E1 48/35</t>
   </si>
   <si>
@@ -276,6 +300,18 @@
   </si>
   <si>
     <t xml:space="preserve">CENTERLINE RED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RT-64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shimano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RT-70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RT-80</t>
   </si>
 </sst>
 </file>
@@ -421,14 +457,15 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="29.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="12.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="38.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="12.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="19.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="9" style="0" width="12.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="19.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1023" min="8" style="0" width="12.63"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="1024" style="0" width="11.52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -450,10 +487,10 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="0" t="s">
         <v>7</v>
       </c>
     </row>
@@ -476,16 +513,19 @@
       <c r="F2" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="H2" s="0" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>5200</v>
@@ -499,16 +539,19 @@
       <c r="F3" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="H3" s="0" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>6000</v>
@@ -522,8 +565,11 @@
       <c r="F4" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="H4" s="0" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -547,12 +593,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="12.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="29.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="6" style="0" width="12.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1023" min="6" style="0" width="12.63"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="1024" style="0" width="11.52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -574,19 +621,19 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="0" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>150</v>
@@ -595,21 +642,24 @@
         <v>198</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>30</v>
       </c>
+      <c r="G2" s="0" t="s">
+        <v>81</v>
+      </c>
       <c r="H2" s="0" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>150</v>
@@ -618,21 +668,24 @@
         <v>188</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>30</v>
       </c>
+      <c r="G3" s="0" t="s">
+        <v>81</v>
+      </c>
       <c r="H3" s="0" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>150</v>
@@ -641,21 +694,104 @@
         <v>168</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>30</v>
       </c>
+      <c r="G4" s="0" t="s">
+        <v>81</v>
+      </c>
       <c r="H4" s="0" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>150</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>198</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="G5" s="0" t="s">
+        <v>81</v>
+      </c>
+      <c r="H5" s="0" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>150</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>188</v>
+      </c>
+      <c r="E6" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="G6" s="0" t="s">
+        <v>81</v>
+      </c>
+      <c r="H6" s="0" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>150</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>168</v>
+      </c>
+      <c r="E7" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="G7" s="0" t="s">
+        <v>81</v>
+      </c>
+      <c r="H7" s="0" t="s">
+        <v>65</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/CadenaOO.png"/>
     <hyperlink ref="E3" r:id="rId2" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/CadenaOO.png"/>
     <hyperlink ref="E4" r:id="rId3" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/CadenaOO.png"/>
+    <hyperlink ref="E5" r:id="rId4" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/CadenaOO.png"/>
+    <hyperlink ref="E6" r:id="rId5" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/CadenaOO.png"/>
+    <hyperlink ref="E7" r:id="rId6" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/CadenaOO.png"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
@@ -672,12 +808,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="12.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="26.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="6" style="0" width="12.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1023" min="6" style="0" width="12.63"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="1024" style="0" width="11.52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -699,19 +836,19 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="0" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>80</v>
@@ -720,21 +857,21 @@
         <v>180</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="H2" s="0" t="s">
-        <v>79</v>
+      <c r="G2" s="0" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>90</v>
@@ -743,21 +880,21 @@
         <v>160</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="H3" s="0" t="s">
-        <v>79</v>
+      <c r="G3" s="0" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>100</v>
@@ -766,13 +903,82 @@
         <v>140</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="H4" s="0" t="s">
-        <v>79</v>
+      <c r="G4" s="0" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>80</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>180</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" s="0" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>92</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>90</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>160</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" s="0" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>140</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" s="0" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -780,6 +986,9 @@
     <hyperlink ref="E2" r:id="rId1" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/DiscsOO.png"/>
     <hyperlink ref="E3" r:id="rId2" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/DiscsOO.png"/>
     <hyperlink ref="E4" r:id="rId3" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/DiscsOO.png"/>
+    <hyperlink ref="E5" r:id="rId4" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/DiscsOO.png"/>
+    <hyperlink ref="E6" r:id="rId5" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/DiscsOO.png"/>
+    <hyperlink ref="E7" r:id="rId6" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/DiscsOO.png"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
@@ -797,11 +1006,12 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="12.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="32.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="6" style="0" width="12.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1023" min="6" style="0" width="12.63"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="1024" style="0" width="11.52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -823,19 +1033,19 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="0" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>2099</v>
@@ -844,21 +1054,21 @@
         <v>1250</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>30</v>
       </c>
-      <c r="H2" s="0" t="s">
-        <v>19</v>
+      <c r="G2" s="0" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>1999</v>
@@ -867,21 +1077,21 @@
         <v>1350</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>30</v>
       </c>
-      <c r="H3" s="0" t="s">
-        <v>19</v>
+      <c r="G3" s="0" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>2599</v>
@@ -890,21 +1100,21 @@
         <v>1450</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>30</v>
       </c>
-      <c r="H4" s="0" t="s">
-        <v>19</v>
+      <c r="G4" s="0" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>1399</v>
@@ -913,13 +1123,13 @@
         <v>1510</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F5" s="0" t="n">
         <v>30</v>
       </c>
-      <c r="H5" s="0" t="s">
-        <v>19</v>
+      <c r="G5" s="0" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -945,11 +1155,12 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="12.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="57.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="6" style="0" width="12.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1023" min="6" style="0" width="12.63"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="1024" style="0" width="11.52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -971,19 +1182,19 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="0" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>160</v>
@@ -992,21 +1203,21 @@
         <v>520</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="H2" s="0" t="s">
-        <v>27</v>
+      <c r="G2" s="0" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>150</v>
@@ -1015,21 +1226,21 @@
         <v>499</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="H3" s="0" t="s">
-        <v>27</v>
+      <c r="G3" s="0" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>180</v>
@@ -1038,21 +1249,21 @@
         <v>560</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="H4" s="0" t="s">
-        <v>27</v>
+      <c r="G4" s="0" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="0" t="s">
         <v>31</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>29</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>170</v>
@@ -1061,13 +1272,13 @@
         <v>550</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F5" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="H5" s="0" t="s">
-        <v>27</v>
+      <c r="G5" s="0" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1092,11 +1303,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="50.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="2" style="0" width="12.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1023" min="2" style="0" width="12.63"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="1024" style="0" width="11.52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1118,19 +1330,19 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="0" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>499</v>
@@ -1139,21 +1351,24 @@
         <v>185</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>10</v>
       </c>
+      <c r="G2" s="0" t="s">
+        <v>37</v>
+      </c>
       <c r="H2" s="0" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>499</v>
@@ -1162,21 +1377,24 @@
         <v>185</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>10</v>
       </c>
+      <c r="G3" s="0" t="s">
+        <v>37</v>
+      </c>
       <c r="H3" s="0" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>499</v>
@@ -1185,44 +1403,50 @@
         <v>185</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>10</v>
       </c>
+      <c r="G4" s="0" t="s">
+        <v>37</v>
+      </c>
       <c r="H4" s="0" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>499</v>
+        <v>599</v>
       </c>
       <c r="D5" s="0" t="n">
         <v>185</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F5" s="0" t="n">
         <v>10</v>
       </c>
+      <c r="G5" s="0" t="s">
+        <v>37</v>
+      </c>
       <c r="H5" s="0" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C6" s="0" t="n">
         <v>499</v>
@@ -1231,44 +1455,50 @@
         <v>185</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F6" s="0" t="n">
         <v>10</v>
       </c>
+      <c r="G6" s="0" t="s">
+        <v>37</v>
+      </c>
       <c r="H6" s="0" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>499</v>
+        <v>599</v>
       </c>
       <c r="D7" s="0" t="n">
         <v>185</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F7" s="0" t="n">
         <v>10</v>
       </c>
+      <c r="G7" s="0" t="s">
+        <v>37</v>
+      </c>
       <c r="H7" s="0" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C8" s="0" t="n">
         <v>499</v>
@@ -1277,21 +1507,24 @@
         <v>185</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F8" s="0" t="n">
         <v>10</v>
       </c>
+      <c r="G8" s="0" t="s">
+        <v>37</v>
+      </c>
       <c r="H8" s="0" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C9" s="0" t="n">
         <v>499</v>
@@ -1300,16 +1533,18 @@
         <v>185</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F9" s="0" t="n">
         <v>10</v>
       </c>
+      <c r="G9" s="0" t="s">
+        <v>37</v>
+      </c>
       <c r="H9" s="0" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/NADA.png"/>
@@ -1340,7 +1575,9 @@
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="25.99"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="2" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="21.55"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="8" style="0" width="11.52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1362,19 +1599,19 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="0" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>34.99</v>
@@ -1383,21 +1620,21 @@
         <v>68</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="H2" s="0" t="s">
-        <v>41</v>
+      <c r="G2" s="0" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="0" t="s">
         <v>42</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>40</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>34.99</v>
@@ -1406,21 +1643,21 @@
         <v>68</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="H3" s="0" t="s">
-        <v>43</v>
+      <c r="G3" s="0" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>34.99</v>
@@ -1429,13 +1666,13 @@
         <v>68</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="H4" s="0" t="s">
-        <v>45</v>
+      <c r="G4" s="0" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1459,7 +1696,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="1" style="0" width="12.63"/>
@@ -1485,18 +1722,21 @@
         <v>5</v>
       </c>
       <c r="G1" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="0" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>120</v>
@@ -1505,21 +1745,21 @@
         <v>190</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>10</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>140</v>
@@ -1528,21 +1768,21 @@
         <v>170</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>10</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>160</v>
@@ -1551,21 +1791,21 @@
         <v>150</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>10</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>180</v>
@@ -1574,21 +1814,21 @@
         <v>135</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F5" s="0" t="n">
         <v>10</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C6" s="0" t="n">
         <v>140</v>
@@ -1597,13 +1837,13 @@
         <v>170</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F6" s="0" t="n">
         <v>10</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1629,10 +1869,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="1" style="0" width="12.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1023" min="1" style="0" width="12.63"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="1024" style="0" width="11.52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1654,19 +1895,19 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="0" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>399</v>
@@ -1675,21 +1916,24 @@
         <v>420</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>30</v>
       </c>
+      <c r="G2" s="0" t="s">
+        <v>59</v>
+      </c>
       <c r="H2" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>499</v>
@@ -1698,21 +1942,24 @@
         <v>390</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>30</v>
       </c>
+      <c r="G3" s="0" t="s">
+        <v>59</v>
+      </c>
       <c r="H3" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>599</v>
@@ -1721,13 +1968,94 @@
         <v>350</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>30</v>
       </c>
+      <c r="G4" s="0" t="s">
+        <v>59</v>
+      </c>
       <c r="H4" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>399</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>420</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="G5" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="H5" s="0" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>499</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>390</v>
+      </c>
+      <c r="E6" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="G6" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="H6" s="0" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>599</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>350</v>
+      </c>
+      <c r="E7" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="G7" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="H7" s="0" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1735,6 +2063,9 @@
     <hyperlink ref="E2" r:id="rId1" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/ForceSHIFTO.png"/>
     <hyperlink ref="E3" r:id="rId2" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/ForceSHIFTO.png"/>
     <hyperlink ref="E4" r:id="rId3" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/ForceSHIFTO.png"/>
+    <hyperlink ref="E5" r:id="rId4" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/ForceSHIFTO.png"/>
+    <hyperlink ref="E6" r:id="rId5" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/ForceSHIFTO.png"/>
+    <hyperlink ref="E7" r:id="rId6" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/ForceSHIFTO.png"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
@@ -1751,13 +2082,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30.32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="12.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="19.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="6" style="0" width="12.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1023" min="6" style="0" width="12.63"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="1024" style="0" width="11.52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1779,19 +2111,19 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="0" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>400</v>
@@ -1800,21 +2132,24 @@
         <v>350</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>60</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>62</v>
+      <c r="G2" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H2" s="0" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>799</v>
@@ -1823,21 +2158,24 @@
         <v>320</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>60</v>
       </c>
-      <c r="H3" s="4" t="s">
-        <v>62</v>
+      <c r="G3" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H3" s="0" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>999</v>
@@ -1846,13 +2184,94 @@
         <v>280</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>60</v>
       </c>
-      <c r="H4" s="4" t="s">
-        <v>62</v>
+      <c r="G4" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H4" s="0" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>400</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>350</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H5" s="0" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>799</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>320</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H6" s="0" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>999</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>280</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H7" s="0" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1860,6 +2279,9 @@
     <hyperlink ref="E2" r:id="rId1" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/ForceCrankOO.png"/>
     <hyperlink ref="E3" r:id="rId2" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/ForceCrankOO.png"/>
     <hyperlink ref="E4" r:id="rId3" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/ForceCrankOO.png"/>
+    <hyperlink ref="E5" r:id="rId4" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/ForceCrankOO.png"/>
+    <hyperlink ref="E6" r:id="rId5" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/ForceCrankOO.png"/>
+    <hyperlink ref="E7" r:id="rId6" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/ForceCrankOO.png"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
@@ -1876,11 +2298,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="2" style="0" width="12.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1023" min="2" style="0" width="12.63"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="1024" style="0" width="11.52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1902,19 +2325,19 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="0" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>449</v>
@@ -1923,21 +2346,24 @@
         <v>420</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>50</v>
       </c>
+      <c r="G2" s="0" t="s">
+        <v>76</v>
+      </c>
       <c r="H2" s="0" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>650</v>
@@ -1946,21 +2372,24 @@
         <v>360</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>50</v>
       </c>
+      <c r="G3" s="0" t="s">
+        <v>76</v>
+      </c>
       <c r="H3" s="0" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>349</v>
@@ -1969,13 +2398,94 @@
         <v>490</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>50</v>
       </c>
+      <c r="G4" s="0" t="s">
+        <v>76</v>
+      </c>
       <c r="H4" s="0" t="s">
-        <v>68</v>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>449</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>420</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="G5" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="H5" s="0" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>650</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>360</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="G6" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="H6" s="0" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>349</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>490</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="G7" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="H7" s="0" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1983,6 +2493,9 @@
     <hyperlink ref="E2" r:id="rId1" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/ForceGroupO.png"/>
     <hyperlink ref="E3" r:id="rId2" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/ForceGroupO.png"/>
     <hyperlink ref="E4" r:id="rId3" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/ForceGroupO.png"/>
+    <hyperlink ref="E5" r:id="rId4" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/ForceGroupO.png"/>
+    <hyperlink ref="E6" r:id="rId5" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/ForceGroupO.png"/>
+    <hyperlink ref="E7" r:id="rId6" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/main/public/parts/ForceGroupO.png"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="Frame" sheetId="1" state="visible" r:id="rId2"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="94">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -56,10 +56,13 @@
     <t xml:space="preserve">Logic</t>
   </si>
   <si>
-    <t xml:space="preserve">S-Works Tarmac SL8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Specialized</t>
+    <t xml:space="preserve">Descripcion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ostro 2,0 WHT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FACTOR</t>
   </si>
   <si>
     <t xml:space="preserve">https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/FrameO.png</t>
@@ -71,19 +74,16 @@
     <t xml:space="preserve">A</t>
   </si>
   <si>
-    <t xml:space="preserve">Madone SLR Gen 7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trek</t>
+    <t xml:space="preserve">This is the best Frame ever made. Just only 685 g and T47BB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ostro 2,0 BLK</t>
   </si>
   <si>
     <t xml:space="preserve">B</t>
   </si>
   <si>
-    <t xml:space="preserve">Lab71 SuperSix EVO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cannondale</t>
+    <t xml:space="preserve">Ostro 2.0 GEO</t>
   </si>
   <si>
     <t xml:space="preserve">ENVE SES</t>
@@ -321,7 +321,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="18">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -345,6 +345,95 @@
       <family val="0"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFCC0000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="10"/>
+      <color rgb="FF808080"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF006600"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="24"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <u val="single"/>
+      <sz val="10"/>
+      <color rgb="FF0000EE"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF996600"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -359,24 +448,58 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
   </fonts>
-  <fills count="2">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF000000"/>
+        <bgColor rgb="FF003300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF808080"/>
+        <bgColor rgb="FF969696"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDDDDD"/>
+        <bgColor rgb="FFFFCCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCCCC"/>
+        <bgColor rgb="FFDDDDDD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC0000"/>
+        <bgColor rgb="FF800000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCFFCC"/>
+        <bgColor rgb="FFCCFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -384,8 +507,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FF808080"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="37">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -409,13 +547,64 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="8" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="8" borderId="1" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -423,7 +612,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -431,23 +620,100 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="23">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Comma" xfId="15" builtinId="3"/>
     <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
     <cellStyle name="Currency" xfId="17" builtinId="4"/>
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="Accent 1 17" xfId="20"/>
+    <cellStyle name="Accent 16" xfId="21"/>
+    <cellStyle name="Accent 2 18" xfId="22"/>
+    <cellStyle name="Accent 3 19" xfId="23"/>
+    <cellStyle name="Bad 13" xfId="24"/>
+    <cellStyle name="Error 15" xfId="25"/>
+    <cellStyle name="Footnote 8" xfId="26"/>
+    <cellStyle name="Good 11" xfId="27"/>
+    <cellStyle name="Heading 1 4" xfId="28"/>
+    <cellStyle name="Heading 2 5" xfId="29"/>
+    <cellStyle name="Heading 3" xfId="30"/>
+    <cellStyle name="Hyperlink 9" xfId="31"/>
+    <cellStyle name="Neutral 12" xfId="32"/>
+    <cellStyle name="Note 7" xfId="33"/>
+    <cellStyle name="Status 10" xfId="34"/>
+    <cellStyle name="Text 6" xfId="35"/>
+    <cellStyle name="Warning 14" xfId="36"/>
   </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFCC0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000EE"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF006600"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF996600"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFDDDDDD"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCCCC"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -456,7 +722,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="29.98"/>
@@ -493,83 +759,89 @@
       <c r="H1" s="0" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="0" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>5500</v>
+        <v>5499</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>685</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>40</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="I2" s="0" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>5200</v>
+        <v>5499</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>750</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>40</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>6000</v>
+        <v>5499</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>770</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>40</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -593,7 +865,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="12.63"/>
@@ -626,6 +898,9 @@
       </c>
       <c r="H1" s="0" t="s">
         <v>7</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -808,12 +1083,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="12.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="26.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1023" min="6" style="0" width="12.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="21.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1023" min="8" style="0" width="12.63"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="1024" style="0" width="11.52"/>
   </cols>
   <sheetData>
@@ -841,6 +1118,9 @@
       </c>
       <c r="H1" s="0" t="s">
         <v>7</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1005,7 +1285,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="12.63"/>
@@ -1038,6 +1318,9 @@
       </c>
       <c r="H1" s="0" t="s">
         <v>7</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1154,7 +1437,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="12.63"/>
@@ -1187,6 +1470,9 @@
       </c>
       <c r="H1" s="0" t="s">
         <v>7</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1303,7 +1589,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="50.63"/>
@@ -1336,6 +1622,9 @@
       <c r="H1" s="0" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="0" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
@@ -1360,7 +1649,7 @@
         <v>37</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1386,7 +1675,7 @@
         <v>37</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1412,7 +1701,7 @@
         <v>37</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1438,7 +1727,7 @@
         <v>37</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1464,7 +1753,7 @@
         <v>37</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1490,7 +1779,7 @@
         <v>37</v>
       </c>
       <c r="H7" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1516,7 +1805,7 @@
         <v>37</v>
       </c>
       <c r="H8" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1542,7 +1831,7 @@
         <v>37</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1571,12 +1860,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="25.99"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="11.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="21.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="21.56"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="8" style="0" width="11.52"/>
   </cols>
   <sheetData>
@@ -1604,6 +1893,9 @@
       </c>
       <c r="H1" s="0" t="s">
         <v>7</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1696,8 +1988,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="1" style="0" width="12.63"/>
   </cols>
@@ -1730,6 +2022,9 @@
       <c r="I1" s="0" t="s">
         <v>7</v>
       </c>
+      <c r="J1" s="0" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
@@ -1748,7 +2043,7 @@
         <v>50</v>
       </c>
       <c r="F2" s="0" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="H2" s="0" t="s">
         <v>51</v>
@@ -1771,7 +2066,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="0" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="H3" s="0" t="s">
         <v>51</v>
@@ -1794,7 +2089,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="0" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="H4" s="0" t="s">
         <v>51</v>
@@ -1817,7 +2112,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="0" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="H5" s="0" t="s">
         <v>51</v>
@@ -1840,7 +2135,7 @@
         <v>50</v>
       </c>
       <c r="F6" s="0" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="H6" s="0" t="s">
         <v>51</v>
@@ -1869,7 +2164,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1023" min="1" style="0" width="12.63"/>
@@ -1901,6 +2196,9 @@
       <c r="H1" s="0" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="0" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
@@ -1919,7 +2217,7 @@
         <v>58</v>
       </c>
       <c r="F2" s="0" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G2" s="0" t="s">
         <v>59</v>
@@ -1945,7 +2243,7 @@
         <v>58</v>
       </c>
       <c r="F3" s="0" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G3" s="0" t="s">
         <v>59</v>
@@ -1971,7 +2269,7 @@
         <v>58</v>
       </c>
       <c r="F4" s="0" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G4" s="0" t="s">
         <v>59</v>
@@ -1997,7 +2295,7 @@
         <v>58</v>
       </c>
       <c r="F5" s="0" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G5" s="0" t="s">
         <v>59</v>
@@ -2023,7 +2321,7 @@
         <v>58</v>
       </c>
       <c r="F6" s="0" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G6" s="0" t="s">
         <v>59</v>
@@ -2049,7 +2347,7 @@
         <v>58</v>
       </c>
       <c r="F7" s="0" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G7" s="0" t="s">
         <v>59</v>
@@ -2082,7 +2380,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30.32"/>
@@ -2116,6 +2414,9 @@
       </c>
       <c r="H1" s="0" t="s">
         <v>7</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2298,7 +2599,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20.37"/>
@@ -2330,6 +2631,9 @@
       </c>
       <c r="H1" s="0" t="s">
         <v>7</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="10"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Frame" sheetId="1" state="visible" r:id="rId2"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="97">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -53,6 +53,15 @@
     <t xml:space="preserve">Cardimg</t>
   </si>
   <si>
+    <t xml:space="preserve">Foto1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foto2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foto3</t>
+  </si>
+  <si>
     <t xml:space="preserve">Logic</t>
   </si>
   <si>
@@ -74,7 +83,35 @@
     <t xml:space="preserve">A</t>
   </si>
   <si>
-    <t xml:space="preserve">This is the best Frame ever made. Just only 685 g and T47BB</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">This is the best Frame ever made. Just only 685 g and T47BB, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">This is the best Frame ever made. Just only 685 g and T47BB, This is the best Frame ever made. Just only 685 g and T47BB, This is the best Frame ever made. Just only 685 g and T47BB, This is the best Frame ever made. Just only 685 g and T47BB, This is the best Frame ever made. Just only 685 g and T47BB, This is the best Frame ever made. Just only 685 g and T47BB, This is the best Frame ever made. Just only 685 g and T47BB, This is the best Frame ever made. Just only 685 g and T47BB, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">Ostro 2,0 BLK</t>
@@ -321,7 +358,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -447,6 +484,12 @@
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
   </fonts>
   <fills count="9">
@@ -612,12 +655,12 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -722,7 +765,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="29.98"/>
@@ -730,8 +773,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="38.44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="19.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1023" min="8" style="0" width="12.63"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="1024" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="8" style="0" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -756,19 +798,28 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>5499</v>
@@ -776,28 +827,37 @@
       <c r="D2" s="1" t="n">
         <v>685</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>11</v>
+      <c r="E2" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="0" t="s">
+      <c r="G2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="L2" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="I2" s="0" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>5499</v>
@@ -805,25 +865,34 @@
       <c r="D3" s="1" t="n">
         <v>750</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>11</v>
+      <c r="E3" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" s="0" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K3" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>5499</v>
@@ -831,17 +900,26 @@
       <c r="D4" s="1" t="n">
         <v>770</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>11</v>
+      <c r="E4" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4" s="0" t="s">
-        <v>13</v>
+      <c r="G4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K4" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -865,13 +943,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="12.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="29.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1023" min="6" style="0" width="12.63"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="1024" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="6" style="0" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -893,22 +970,31 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>150</v>
@@ -917,24 +1003,24 @@
         <v>198</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>30</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>81</v>
-      </c>
-      <c r="H2" s="0" t="s">
-        <v>60</v>
+        <v>84</v>
+      </c>
+      <c r="K2" s="0" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>150</v>
@@ -943,24 +1029,24 @@
         <v>188</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>30</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>81</v>
-      </c>
-      <c r="H3" s="0" t="s">
-        <v>60</v>
+        <v>84</v>
+      </c>
+      <c r="K3" s="0" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>150</v>
@@ -969,24 +1055,24 @@
         <v>168</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>30</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>81</v>
-      </c>
-      <c r="H4" s="0" t="s">
-        <v>60</v>
+        <v>84</v>
+      </c>
+      <c r="K4" s="0" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>150</v>
@@ -995,24 +1081,24 @@
         <v>198</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F5" s="0" t="n">
         <v>30</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>81</v>
-      </c>
-      <c r="H5" s="0" t="s">
-        <v>65</v>
+        <v>84</v>
+      </c>
+      <c r="K5" s="0" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C6" s="0" t="n">
         <v>150</v>
@@ -1021,24 +1107,24 @@
         <v>188</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F6" s="0" t="n">
         <v>30</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>81</v>
-      </c>
-      <c r="H6" s="0" t="s">
-        <v>65</v>
+        <v>84</v>
+      </c>
+      <c r="K6" s="0" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" s="0" t="s">
         <v>67</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>64</v>
       </c>
       <c r="C7" s="0" t="n">
         <v>150</v>
@@ -1047,16 +1133,16 @@
         <v>168</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F7" s="0" t="n">
         <v>30</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>81</v>
-      </c>
-      <c r="H7" s="0" t="s">
-        <v>65</v>
+        <v>84</v>
+      </c>
+      <c r="K7" s="0" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -1083,15 +1169,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="12.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="26.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="21.97"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1023" min="8" style="0" width="12.63"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="1024" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="8" style="0" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1113,22 +1198,31 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>80</v>
@@ -1137,21 +1231,21 @@
         <v>180</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>10</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="B3" s="0" t="s">
         <v>88</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>85</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>90</v>
@@ -1160,21 +1254,21 @@
         <v>160</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>10</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>100</v>
@@ -1183,21 +1277,21 @@
         <v>140</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>10</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>80</v>
@@ -1206,21 +1300,21 @@
         <v>180</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F5" s="0" t="n">
         <v>10</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C6" s="0" t="n">
         <v>90</v>
@@ -1229,21 +1323,21 @@
         <v>160</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F6" s="0" t="n">
         <v>10</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C7" s="0" t="n">
         <v>100</v>
@@ -1252,13 +1346,13 @@
         <v>140</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F7" s="0" t="n">
         <v>10</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -1285,13 +1379,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="12.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="32.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1023" min="6" style="0" width="12.63"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="1024" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="6" style="0" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1313,22 +1406,31 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>2099</v>
@@ -1337,21 +1439,21 @@
         <v>1250</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>30</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>1999</v>
@@ -1360,21 +1462,21 @@
         <v>1350</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>30</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>2599</v>
@@ -1383,21 +1485,21 @@
         <v>1450</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>30</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>1399</v>
@@ -1406,13 +1508,13 @@
         <v>1510</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F5" s="0" t="n">
         <v>30</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1437,13 +1539,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="12.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="57.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1023" min="6" style="0" width="12.63"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="1024" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="6" style="0" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1465,22 +1566,31 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>160</v>
@@ -1489,21 +1599,21 @@
         <v>520</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>20</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>150</v>
@@ -1512,21 +1622,21 @@
         <v>499</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>20</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>180</v>
@@ -1535,21 +1645,21 @@
         <v>560</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>20</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>170</v>
@@ -1558,13 +1668,13 @@
         <v>550</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F5" s="0" t="n">
         <v>20</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1589,12 +1699,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="50.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1023" min="2" style="0" width="12.63"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="1024" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="2" style="0" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1616,22 +1725,31 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>499</v>
@@ -1640,24 +1758,24 @@
         <v>185</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>10</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="H2" s="0" t="s">
-        <v>13</v>
+        <v>40</v>
+      </c>
+      <c r="K2" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="0" t="s">
         <v>38</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>35</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>499</v>
@@ -1666,24 +1784,24 @@
         <v>185</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>10</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="H3" s="0" t="s">
-        <v>13</v>
+        <v>40</v>
+      </c>
+      <c r="K3" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>499</v>
@@ -1692,24 +1810,24 @@
         <v>185</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>10</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="H4" s="0" t="s">
-        <v>13</v>
+        <v>40</v>
+      </c>
+      <c r="K4" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>599</v>
@@ -1718,24 +1836,24 @@
         <v>185</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F5" s="0" t="n">
         <v>10</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="H5" s="0" t="s">
-        <v>16</v>
+        <v>40</v>
+      </c>
+      <c r="K5" s="0" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C6" s="0" t="n">
         <v>499</v>
@@ -1744,24 +1862,24 @@
         <v>185</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F6" s="0" t="n">
         <v>10</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="H6" s="0" t="s">
-        <v>13</v>
+        <v>40</v>
+      </c>
+      <c r="K6" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="0" t="s">
         <v>38</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>35</v>
       </c>
       <c r="C7" s="0" t="n">
         <v>599</v>
@@ -1770,24 +1888,24 @@
         <v>185</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F7" s="0" t="n">
         <v>10</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="H7" s="0" t="s">
-        <v>16</v>
+        <v>40</v>
+      </c>
+      <c r="K7" s="0" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C8" s="0" t="n">
         <v>499</v>
@@ -1796,24 +1914,24 @@
         <v>185</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F8" s="0" t="n">
         <v>10</v>
       </c>
       <c r="G8" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="H8" s="0" t="s">
-        <v>13</v>
+        <v>40</v>
+      </c>
+      <c r="K8" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C9" s="0" t="n">
         <v>499</v>
@@ -1822,16 +1940,16 @@
         <v>185</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F9" s="0" t="n">
         <v>10</v>
       </c>
       <c r="G9" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="H9" s="0" t="s">
-        <v>13</v>
+        <v>40</v>
+      </c>
+      <c r="K9" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1860,7 +1978,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="25.99"/>
@@ -1888,22 +2006,31 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>34.99</v>
@@ -1912,21 +2039,21 @@
         <v>68</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>10</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>34.99</v>
@@ -1935,21 +2062,21 @@
         <v>68</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>10</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>34.99</v>
@@ -1958,13 +2085,13 @@
         <v>68</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>10</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1988,7 +2115,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="1" style="0" width="12.63"/>
@@ -2014,24 +2141,33 @@
         <v>5</v>
       </c>
       <c r="G1" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>120</v>
@@ -2040,21 +2176,21 @@
         <v>190</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>50</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="0" t="s">
         <v>52</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>49</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>140</v>
@@ -2063,21 +2199,21 @@
         <v>170</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>50</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>160</v>
@@ -2086,21 +2222,21 @@
         <v>150</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>50</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>180</v>
@@ -2109,21 +2245,21 @@
         <v>135</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F5" s="0" t="n">
         <v>50</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C6" s="0" t="n">
         <v>140</v>
@@ -2132,13 +2268,13 @@
         <v>170</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F6" s="0" t="n">
         <v>50</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -2164,11 +2300,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1023" min="1" style="0" width="12.63"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="1024" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="1" style="0" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2190,22 +2325,31 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>399</v>
@@ -2214,24 +2358,24 @@
         <v>420</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>50</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="H2" s="0" t="s">
-        <v>60</v>
+        <v>62</v>
+      </c>
+      <c r="K2" s="0" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>499</v>
@@ -2240,24 +2384,24 @@
         <v>390</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>50</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="H3" s="0" t="s">
-        <v>60</v>
+        <v>62</v>
+      </c>
+      <c r="K3" s="0" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>599</v>
@@ -2266,24 +2410,24 @@
         <v>350</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>50</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="H4" s="0" t="s">
-        <v>60</v>
+        <v>62</v>
+      </c>
+      <c r="K4" s="0" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>399</v>
@@ -2292,24 +2436,24 @@
         <v>420</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F5" s="0" t="n">
         <v>50</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="H5" s="0" t="s">
-        <v>65</v>
+        <v>62</v>
+      </c>
+      <c r="K5" s="0" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C6" s="0" t="n">
         <v>499</v>
@@ -2318,24 +2462,24 @@
         <v>390</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F6" s="0" t="n">
         <v>50</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="H6" s="0" t="s">
-        <v>65</v>
+        <v>62</v>
+      </c>
+      <c r="K6" s="0" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" s="0" t="s">
         <v>67</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>64</v>
       </c>
       <c r="C7" s="0" t="n">
         <v>599</v>
@@ -2344,16 +2488,16 @@
         <v>350</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F7" s="0" t="n">
         <v>50</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="H7" s="0" t="s">
-        <v>65</v>
+        <v>62</v>
+      </c>
+      <c r="K7" s="0" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -2380,14 +2524,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30.32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="12.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="19.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1023" min="6" style="0" width="12.63"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="1024" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="6" style="0" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2409,22 +2552,31 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>400</v>
@@ -2433,24 +2585,27 @@
         <v>350</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>60</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="H2" s="0" t="s">
-        <v>60</v>
+      <c r="G2" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="0" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>799</v>
@@ -2459,24 +2614,27 @@
         <v>320</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>60</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="H3" s="0" t="s">
-        <v>60</v>
+      <c r="G3" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="0" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>999</v>
@@ -2485,24 +2643,27 @@
         <v>280</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>60</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="H4" s="0" t="s">
-        <v>60</v>
+      <c r="G4" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="0" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>400</v>
@@ -2511,24 +2672,27 @@
         <v>350</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F5" s="0" t="n">
         <v>60</v>
       </c>
-      <c r="G5" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="H5" s="0" t="s">
-        <v>65</v>
+      <c r="G5" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="0" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C6" s="0" t="n">
         <v>799</v>
@@ -2537,24 +2701,27 @@
         <v>320</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F6" s="0" t="n">
         <v>60</v>
       </c>
-      <c r="G6" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="H6" s="0" t="s">
-        <v>65</v>
+      <c r="G6" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="0" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" s="0" t="s">
         <v>67</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>64</v>
       </c>
       <c r="C7" s="0" t="n">
         <v>999</v>
@@ -2563,16 +2730,19 @@
         <v>280</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F7" s="0" t="n">
         <v>60</v>
       </c>
-      <c r="G7" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="H7" s="0" t="s">
-        <v>65</v>
+      <c r="G7" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="0" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -2599,12 +2769,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1023" min="2" style="0" width="12.63"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="1024" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="2" style="0" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2626,22 +2795,31 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>449</v>
@@ -2649,25 +2827,25 @@
       <c r="D2" s="0" t="n">
         <v>420</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>75</v>
+      <c r="E2" s="3" t="s">
+        <v>78</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>50</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>76</v>
-      </c>
-      <c r="H2" s="0" t="s">
-        <v>60</v>
+        <v>79</v>
+      </c>
+      <c r="K2" s="0" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3" s="0" t="s">
         <v>77</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>74</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>650</v>
@@ -2675,25 +2853,25 @@
       <c r="D3" s="0" t="n">
         <v>360</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>75</v>
+      <c r="E3" s="3" t="s">
+        <v>78</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>50</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>76</v>
-      </c>
-      <c r="H3" s="0" t="s">
-        <v>60</v>
+        <v>79</v>
+      </c>
+      <c r="K3" s="0" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>349</v>
@@ -2701,25 +2879,25 @@
       <c r="D4" s="0" t="n">
         <v>490</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>75</v>
+      <c r="E4" s="3" t="s">
+        <v>78</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>50</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>76</v>
-      </c>
-      <c r="H4" s="0" t="s">
-        <v>60</v>
+        <v>79</v>
+      </c>
+      <c r="K4" s="0" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>449</v>
@@ -2727,25 +2905,25 @@
       <c r="D5" s="0" t="n">
         <v>420</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>75</v>
+      <c r="E5" s="3" t="s">
+        <v>78</v>
       </c>
       <c r="F5" s="0" t="n">
         <v>50</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>76</v>
-      </c>
-      <c r="H5" s="0" t="s">
-        <v>65</v>
+        <v>79</v>
+      </c>
+      <c r="K5" s="0" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C6" s="0" t="n">
         <v>650</v>
@@ -2753,25 +2931,25 @@
       <c r="D6" s="0" t="n">
         <v>360</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>75</v>
+      <c r="E6" s="3" t="s">
+        <v>78</v>
       </c>
       <c r="F6" s="0" t="n">
         <v>50</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>76</v>
-      </c>
-      <c r="H6" s="0" t="s">
-        <v>65</v>
+        <v>79</v>
+      </c>
+      <c r="K6" s="0" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" s="0" t="s">
         <v>67</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>64</v>
       </c>
       <c r="C7" s="0" t="n">
         <v>349</v>
@@ -2779,17 +2957,17 @@
       <c r="D7" s="0" t="n">
         <v>490</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>75</v>
+      <c r="E7" s="3" t="s">
+        <v>78</v>
       </c>
       <c r="F7" s="0" t="n">
         <v>50</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>76</v>
-      </c>
-      <c r="H7" s="0" t="s">
-        <v>65</v>
+        <v>79</v>
+      </c>
+      <c r="K7" s="0" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="101">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -83,35 +83,7 @@
     <t xml:space="preserve">A</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">This is the best Frame ever made. Just only 685 g and T47BB, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">This is the best Frame ever made. Just only 685 g and T47BB, This is the best Frame ever made. Just only 685 g and T47BB, This is the best Frame ever made. Just only 685 g and T47BB, This is the best Frame ever made. Just only 685 g and T47BB, This is the best Frame ever made. Just only 685 g and T47BB, This is the best Frame ever made. Just only 685 g and T47BB, This is the best Frame ever made. Just only 685 g and T47BB, This is the best Frame ever made. Just only 685 g and T47BB, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
+    <t xml:space="preserve">This is the best Frame ever made. Just only 685 g and T47BB, This is the best Frame ever made. Just only 685 g and T47BB, This is the best Frame ever made. Just only 685 g and T47BB, This is the best Frame ever made. Just only 685 g and T47BB, This is the best Frame ever made. Just only 685 g and T47BB, This is the best Frame ever made. Just only 685 g and T47BB, This is the best Frame ever made. Just only 685 g and T47BB, This is the best Frame ever made. Just only 685 g and T47BB, This is the best Frame ever made. Just only 685 g and T47BB,  </t>
   </si>
   <si>
     <t xml:space="preserve">Ostro 2,0 BLK</t>
@@ -121,6 +93,18 @@
   </si>
   <si>
     <t xml:space="preserve">Ostro 2.0 GEO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One Silverstone </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/Frame/One_Silverstone.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/parts/Frame/One_Silverstone.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/p</t>
   </si>
   <si>
     <t xml:space="preserve">ENVE SES</t>
@@ -486,6 +470,7 @@
       <charset val="1"/>
     </font>
     <font>
+      <u val="single"/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -642,7 +627,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -661,6 +646,10 @@
     </xf>
     <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -765,7 +754,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="29.98"/>
@@ -920,6 +909,46 @@
       </c>
       <c r="K4" s="0" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>5499</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>950</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>40</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I8" s="5"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E9" s="5" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -991,10 +1020,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>150</v>
@@ -1003,24 +1032,24 @@
         <v>198</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>30</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="K2" s="0" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>150</v>
@@ -1029,24 +1058,24 @@
         <v>188</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>30</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="K3" s="0" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>150</v>
@@ -1055,24 +1084,24 @@
         <v>168</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>30</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="K4" s="0" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>150</v>
@@ -1081,24 +1110,24 @@
         <v>198</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F5" s="0" t="n">
         <v>30</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="K5" s="0" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C6" s="0" t="n">
         <v>150</v>
@@ -1107,24 +1136,24 @@
         <v>188</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F6" s="0" t="n">
         <v>30</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="K6" s="0" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C7" s="0" t="n">
         <v>150</v>
@@ -1133,16 +1162,16 @@
         <v>168</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F7" s="0" t="n">
         <v>30</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="K7" s="0" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1219,10 +1248,10 @@
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>80</v>
@@ -1230,22 +1259,22 @@
       <c r="D2" s="0" t="n">
         <v>180</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>89</v>
+      <c r="E2" s="6" t="s">
+        <v>93</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>10</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>90</v>
@@ -1253,22 +1282,22 @@
       <c r="D3" s="0" t="n">
         <v>160</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>89</v>
+      <c r="E3" s="6" t="s">
+        <v>93</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>10</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" s="0" t="s">
         <v>92</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>88</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>100</v>
@@ -1276,22 +1305,22 @@
       <c r="D4" s="0" t="n">
         <v>140</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>89</v>
+      <c r="E4" s="6" t="s">
+        <v>93</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>10</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>80</v>
@@ -1299,22 +1328,22 @@
       <c r="D5" s="0" t="n">
         <v>180</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>89</v>
+      <c r="E5" s="6" t="s">
+        <v>93</v>
       </c>
       <c r="F5" s="0" t="n">
         <v>10</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C6" s="0" t="n">
         <v>90</v>
@@ -1322,22 +1351,22 @@
       <c r="D6" s="0" t="n">
         <v>160</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>89</v>
+      <c r="E6" s="6" t="s">
+        <v>93</v>
       </c>
       <c r="F6" s="0" t="n">
         <v>10</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C7" s="0" t="n">
         <v>100</v>
@@ -1345,14 +1374,14 @@
       <c r="D7" s="0" t="n">
         <v>140</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>89</v>
+      <c r="E7" s="6" t="s">
+        <v>93</v>
       </c>
       <c r="F7" s="0" t="n">
         <v>10</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -1427,10 +1456,10 @@
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>2099</v>
@@ -1438,22 +1467,22 @@
       <c r="D2" s="0" t="n">
         <v>1250</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>23</v>
+      <c r="E2" s="6" t="s">
+        <v>27</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>30</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>1999</v>
@@ -1461,22 +1490,22 @@
       <c r="D3" s="0" t="n">
         <v>1350</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>23</v>
+      <c r="E3" s="6" t="s">
+        <v>27</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>30</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>2599</v>
@@ -1484,22 +1513,22 @@
       <c r="D4" s="0" t="n">
         <v>1450</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>23</v>
+      <c r="E4" s="6" t="s">
+        <v>27</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>30</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>1399</v>
@@ -1507,14 +1536,14 @@
       <c r="D5" s="0" t="n">
         <v>1510</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>23</v>
+      <c r="E5" s="6" t="s">
+        <v>27</v>
       </c>
       <c r="F5" s="0" t="n">
         <v>30</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1587,10 +1616,10 @@
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>160</v>
@@ -1598,22 +1627,22 @@
       <c r="D2" s="0" t="n">
         <v>520</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>31</v>
+      <c r="E2" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>20</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>150</v>
@@ -1621,22 +1650,22 @@
       <c r="D3" s="0" t="n">
         <v>499</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>31</v>
+      <c r="E3" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>20</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>180</v>
@@ -1644,22 +1673,22 @@
       <c r="D4" s="0" t="n">
         <v>560</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>31</v>
+      <c r="E4" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>20</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>170</v>
@@ -1667,14 +1696,14 @@
       <c r="D5" s="0" t="n">
         <v>550</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>31</v>
+      <c r="E5" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="F5" s="0" t="n">
         <v>20</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1746,10 +1775,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>499</v>
@@ -1758,13 +1787,13 @@
         <v>185</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>10</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="K2" s="0" t="s">
         <v>16</v>
@@ -1772,10 +1801,10 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>499</v>
@@ -1784,13 +1813,13 @@
         <v>185</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>10</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="K3" s="0" t="s">
         <v>16</v>
@@ -1798,10 +1827,10 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="0" t="s">
         <v>42</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>38</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>499</v>
@@ -1810,13 +1839,13 @@
         <v>185</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>10</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="K4" s="0" t="s">
         <v>16</v>
@@ -1824,10 +1853,10 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>599</v>
@@ -1836,13 +1865,13 @@
         <v>185</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F5" s="0" t="n">
         <v>10</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="K5" s="0" t="s">
         <v>19</v>
@@ -1850,10 +1879,10 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C6" s="0" t="n">
         <v>499</v>
@@ -1862,13 +1891,13 @@
         <v>185</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F6" s="0" t="n">
         <v>10</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="K6" s="0" t="s">
         <v>16</v>
@@ -1876,10 +1905,10 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C7" s="0" t="n">
         <v>599</v>
@@ -1888,13 +1917,13 @@
         <v>185</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F7" s="0" t="n">
         <v>10</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="K7" s="0" t="s">
         <v>19</v>
@@ -1902,10 +1931,10 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="0" t="s">
         <v>42</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>38</v>
       </c>
       <c r="C8" s="0" t="n">
         <v>499</v>
@@ -1914,13 +1943,13 @@
         <v>185</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F8" s="0" t="n">
         <v>10</v>
       </c>
       <c r="G8" s="0" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="K8" s="0" t="s">
         <v>16</v>
@@ -1928,10 +1957,10 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C9" s="0" t="n">
         <v>499</v>
@@ -1940,13 +1969,13 @@
         <v>185</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F9" s="0" t="n">
         <v>10</v>
       </c>
       <c r="G9" s="0" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="K9" s="0" t="s">
         <v>16</v>
@@ -2027,10 +2056,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>34.99</v>
@@ -2039,21 +2068,21 @@
         <v>68</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>10</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>34.99</v>
@@ -2062,21 +2091,21 @@
         <v>68</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>10</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="0" t="s">
         <v>49</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>45</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>34.99</v>
@@ -2085,13 +2114,13 @@
         <v>68</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>10</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -2164,10 +2193,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>120</v>
@@ -2176,21 +2205,21 @@
         <v>190</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>50</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>140</v>
@@ -2199,21 +2228,21 @@
         <v>170</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>50</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="0" t="s">
         <v>56</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>52</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>160</v>
@@ -2222,21 +2251,21 @@
         <v>150</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>50</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>180</v>
@@ -2245,21 +2274,21 @@
         <v>135</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F5" s="0" t="n">
         <v>50</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C6" s="0" t="n">
         <v>140</v>
@@ -2268,13 +2297,13 @@
         <v>170</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F6" s="0" t="n">
         <v>50</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -2346,10 +2375,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>399</v>
@@ -2358,24 +2387,24 @@
         <v>420</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>50</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="K2" s="0" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="B3" s="0" t="s">
         <v>64</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>60</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>499</v>
@@ -2384,24 +2413,24 @@
         <v>390</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>50</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="K3" s="0" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>599</v>
@@ -2410,24 +2439,24 @@
         <v>350</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>50</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="K4" s="0" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>399</v>
@@ -2436,24 +2465,24 @@
         <v>420</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F5" s="0" t="n">
         <v>50</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="K5" s="0" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C6" s="0" t="n">
         <v>499</v>
@@ -2462,24 +2491,24 @@
         <v>390</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F6" s="0" t="n">
         <v>50</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="K6" s="0" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C7" s="0" t="n">
         <v>599</v>
@@ -2488,16 +2517,16 @@
         <v>350</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F7" s="0" t="n">
         <v>50</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="K7" s="0" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2573,10 +2602,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>400</v>
@@ -2584,28 +2613,28 @@
       <c r="D2" s="0" t="n">
         <v>350</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>72</v>
+      <c r="E2" s="7" t="s">
+        <v>76</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>60</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="0" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>799</v>
@@ -2613,28 +2642,28 @@
       <c r="D3" s="0" t="n">
         <v>320</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>72</v>
+      <c r="E3" s="7" t="s">
+        <v>76</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>60</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="0" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>999</v>
@@ -2642,28 +2671,28 @@
       <c r="D4" s="0" t="n">
         <v>280</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>72</v>
+      <c r="E4" s="7" t="s">
+        <v>76</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>60</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
       <c r="K4" s="0" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>400</v>
@@ -2671,28 +2700,28 @@
       <c r="D5" s="0" t="n">
         <v>350</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>72</v>
+      <c r="E5" s="7" t="s">
+        <v>76</v>
       </c>
       <c r="F5" s="0" t="n">
         <v>60</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
       <c r="K5" s="0" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C6" s="0" t="n">
         <v>799</v>
@@ -2700,28 +2729,28 @@
       <c r="D6" s="0" t="n">
         <v>320</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>72</v>
+      <c r="E6" s="7" t="s">
+        <v>76</v>
       </c>
       <c r="F6" s="0" t="n">
         <v>60</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="0" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C7" s="0" t="n">
         <v>999</v>
@@ -2729,20 +2758,20 @@
       <c r="D7" s="0" t="n">
         <v>280</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>72</v>
+      <c r="E7" s="7" t="s">
+        <v>76</v>
       </c>
       <c r="F7" s="0" t="n">
         <v>60</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
       <c r="K7" s="0" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2816,10 +2845,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>449</v>
@@ -2828,24 +2857,24 @@
         <v>420</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>50</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K2" s="0" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>650</v>
@@ -2854,24 +2883,24 @@
         <v>360</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>50</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K3" s="0" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="B4" s="0" t="s">
         <v>81</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>77</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>349</v>
@@ -2880,24 +2909,24 @@
         <v>490</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>50</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K4" s="0" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>449</v>
@@ -2906,24 +2935,24 @@
         <v>420</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F5" s="0" t="n">
         <v>50</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K5" s="0" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C6" s="0" t="n">
         <v>650</v>
@@ -2932,24 +2961,24 @@
         <v>360</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F6" s="0" t="n">
         <v>50</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K6" s="0" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C7" s="0" t="n">
         <v>349</v>
@@ -2958,16 +2987,16 @@
         <v>490</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F7" s="0" t="n">
         <v>50</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K7" s="0" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="100">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -102,9 +102,6 @@
   </si>
   <si>
     <t xml:space="preserve">/parts/Frame/One_Silverstone.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/p</t>
   </si>
   <si>
     <t xml:space="preserve">ENVE SES</t>
@@ -342,7 +339,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="18">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -468,13 +465,6 @@
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <u val="single"/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
   </fonts>
   <fills count="9">
@@ -648,7 +638,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -754,7 +744,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="29.98"/>
@@ -911,51 +901,53 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B5" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="0" t="n">
+      <c r="C5" s="0" t="n">
         <v>5499</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D5" s="0" t="n">
         <v>950</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="F5" s="0" t="n">
         <v>40</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G5" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H5" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="I5" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="J5" s="5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I8" s="5"/>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E9" s="5" t="s">
-        <v>24</v>
-      </c>
+      <c r="K5" s="0" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I6" s="5"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E7" s="5"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/FrameO.png"/>
     <hyperlink ref="E3" r:id="rId2" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/FrameO.png"/>
     <hyperlink ref="E4" r:id="rId3" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/FrameO.png"/>
+    <hyperlink ref="E5" r:id="rId4" display="https://raw.githubusercontent.com/VasileAdicto/Adictobike/refs/heads/main/public/parts/Frame/One_Silverstone.png"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
@@ -1020,10 +1012,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>150</v>
@@ -1032,24 +1024,24 @@
         <v>198</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>30</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K2" s="0" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>150</v>
@@ -1058,24 +1050,24 @@
         <v>188</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>30</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K3" s="0" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>150</v>
@@ -1084,24 +1076,24 @@
         <v>168</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>30</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K4" s="0" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" s="0" t="s">
         <v>70</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>71</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>150</v>
@@ -1110,24 +1102,24 @@
         <v>198</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F5" s="0" t="n">
         <v>30</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K5" s="0" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C6" s="0" t="n">
         <v>150</v>
@@ -1136,24 +1128,24 @@
         <v>188</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F6" s="0" t="n">
         <v>30</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K6" s="0" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C7" s="0" t="n">
         <v>150</v>
@@ -1162,16 +1154,16 @@
         <v>168</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F7" s="0" t="n">
         <v>30</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K7" s="0" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1248,10 +1240,10 @@
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="B2" s="0" t="s">
         <v>91</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>92</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>80</v>
@@ -1260,21 +1252,21 @@
         <v>180</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>10</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>90</v>
@@ -1283,21 +1275,21 @@
         <v>160</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>10</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>100</v>
@@ -1306,21 +1298,21 @@
         <v>140</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>10</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="B5" s="0" t="s">
         <v>97</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>98</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>80</v>
@@ -1329,21 +1321,21 @@
         <v>180</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F5" s="0" t="n">
         <v>10</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C6" s="0" t="n">
         <v>90</v>
@@ -1352,21 +1344,21 @@
         <v>160</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F6" s="0" t="n">
         <v>10</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C7" s="0" t="n">
         <v>100</v>
@@ -1375,13 +1367,13 @@
         <v>140</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F7" s="0" t="n">
         <v>10</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1456,10 +1448,10 @@
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="0" t="s">
         <v>25</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>26</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>2099</v>
@@ -1468,21 +1460,21 @@
         <v>1250</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>30</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="0" t="s">
         <v>29</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>30</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>1999</v>
@@ -1491,21 +1483,21 @@
         <v>1350</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>30</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>2599</v>
@@ -1514,21 +1506,21 @@
         <v>1450</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>30</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>1399</v>
@@ -1537,13 +1529,13 @@
         <v>1510</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F5" s="0" t="n">
         <v>30</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1616,10 +1608,10 @@
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="0" t="s">
         <v>33</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>34</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>160</v>
@@ -1628,21 +1620,21 @@
         <v>520</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>20</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="0" t="s">
         <v>37</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>38</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>150</v>
@@ -1651,21 +1643,21 @@
         <v>499</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>20</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>180</v>
@@ -1674,21 +1666,21 @@
         <v>560</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>20</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>170</v>
@@ -1697,13 +1689,13 @@
         <v>550</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F5" s="0" t="n">
         <v>20</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1775,10 +1767,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="0" t="s">
         <v>41</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>42</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>499</v>
@@ -1787,13 +1779,13 @@
         <v>185</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>10</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K2" s="0" t="s">
         <v>16</v>
@@ -1801,10 +1793,10 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>499</v>
@@ -1813,13 +1805,13 @@
         <v>185</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>10</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K3" s="0" t="s">
         <v>16</v>
@@ -1827,10 +1819,10 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>499</v>
@@ -1839,13 +1831,13 @@
         <v>185</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>10</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K4" s="0" t="s">
         <v>16</v>
@@ -1853,10 +1845,10 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>599</v>
@@ -1865,13 +1857,13 @@
         <v>185</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F5" s="0" t="n">
         <v>10</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K5" s="0" t="s">
         <v>19</v>
@@ -1879,10 +1871,10 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="0" t="s">
         <v>41</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>42</v>
       </c>
       <c r="C6" s="0" t="n">
         <v>499</v>
@@ -1891,13 +1883,13 @@
         <v>185</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F6" s="0" t="n">
         <v>10</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K6" s="0" t="s">
         <v>16</v>
@@ -1905,10 +1897,10 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C7" s="0" t="n">
         <v>599</v>
@@ -1917,13 +1909,13 @@
         <v>185</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F7" s="0" t="n">
         <v>10</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K7" s="0" t="s">
         <v>19</v>
@@ -1931,10 +1923,10 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C8" s="0" t="n">
         <v>499</v>
@@ -1943,13 +1935,13 @@
         <v>185</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F8" s="0" t="n">
         <v>10</v>
       </c>
       <c r="G8" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K8" s="0" t="s">
         <v>16</v>
@@ -1957,10 +1949,10 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C9" s="0" t="n">
         <v>499</v>
@@ -1969,13 +1961,13 @@
         <v>185</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F9" s="0" t="n">
         <v>10</v>
       </c>
       <c r="G9" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K9" s="0" t="s">
         <v>16</v>
@@ -2056,10 +2048,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="0" t="s">
         <v>48</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>49</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>34.99</v>
@@ -2068,21 +2060,21 @@
         <v>68</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>10</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>34.99</v>
@@ -2091,21 +2083,21 @@
         <v>68</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>10</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>34.99</v>
@@ -2114,13 +2106,13 @@
         <v>68</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>10</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -2193,10 +2185,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="0" t="s">
         <v>55</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>56</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>120</v>
@@ -2205,21 +2197,21 @@
         <v>190</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>50</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>140</v>
@@ -2228,21 +2220,21 @@
         <v>170</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>50</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>160</v>
@@ -2251,21 +2243,21 @@
         <v>150</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>50</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>180</v>
@@ -2274,21 +2266,21 @@
         <v>135</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F5" s="0" t="n">
         <v>50</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C6" s="0" t="n">
         <v>140</v>
@@ -2297,13 +2289,13 @@
         <v>170</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F6" s="0" t="n">
         <v>50</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -2375,10 +2367,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" s="0" t="s">
         <v>63</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>64</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>399</v>
@@ -2387,24 +2379,24 @@
         <v>420</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>50</v>
       </c>
       <c r="G2" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="K2" s="0" t="s">
         <v>66</v>
-      </c>
-      <c r="K2" s="0" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>499</v>
@@ -2413,24 +2405,24 @@
         <v>390</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>50</v>
       </c>
       <c r="G3" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="K3" s="0" t="s">
         <v>66</v>
-      </c>
-      <c r="K3" s="0" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>599</v>
@@ -2439,24 +2431,24 @@
         <v>350</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>50</v>
       </c>
       <c r="G4" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="K4" s="0" t="s">
         <v>66</v>
-      </c>
-      <c r="K4" s="0" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" s="0" t="s">
         <v>70</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>71</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>399</v>
@@ -2465,24 +2457,24 @@
         <v>420</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F5" s="0" t="n">
         <v>50</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K5" s="0" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C6" s="0" t="n">
         <v>499</v>
@@ -2491,24 +2483,24 @@
         <v>390</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F6" s="0" t="n">
         <v>50</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K6" s="0" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C7" s="0" t="n">
         <v>599</v>
@@ -2517,16 +2509,16 @@
         <v>350</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F7" s="0" t="n">
         <v>50</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K7" s="0" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -2602,10 +2594,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>400</v>
@@ -2614,27 +2606,27 @@
         <v>350</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>60</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="0" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>799</v>
@@ -2643,27 +2635,27 @@
         <v>320</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>60</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="0" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>999</v>
@@ -2672,27 +2664,27 @@
         <v>280</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>60</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
       <c r="K4" s="0" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" s="0" t="s">
         <v>70</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>71</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>400</v>
@@ -2701,27 +2693,27 @@
         <v>350</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F5" s="0" t="n">
         <v>60</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
       <c r="K5" s="0" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C6" s="0" t="n">
         <v>799</v>
@@ -2730,27 +2722,27 @@
         <v>320</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F6" s="0" t="n">
         <v>60</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="0" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C7" s="0" t="n">
         <v>999</v>
@@ -2759,19 +2751,19 @@
         <v>280</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F7" s="0" t="n">
         <v>60</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
       <c r="K7" s="0" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -2845,10 +2837,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="B2" s="0" t="s">
         <v>80</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>81</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>449</v>
@@ -2857,24 +2849,24 @@
         <v>420</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>50</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K2" s="0" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>650</v>
@@ -2883,24 +2875,24 @@
         <v>360</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>50</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K3" s="0" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>349</v>
@@ -2909,24 +2901,24 @@
         <v>490</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>50</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K4" s="0" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" s="0" t="s">
         <v>70</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>71</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>449</v>
@@ -2935,24 +2927,24 @@
         <v>420</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F5" s="0" t="n">
         <v>50</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K5" s="0" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C6" s="0" t="n">
         <v>650</v>
@@ -2961,24 +2953,24 @@
         <v>360</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F6" s="0" t="n">
         <v>50</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K6" s="0" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C7" s="0" t="n">
         <v>349</v>
@@ -2987,16 +2979,16 @@
         <v>490</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F7" s="0" t="n">
         <v>50</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K7" s="0" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
